--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richi\AppData\Local\Temp\mx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42BD17A9-959F-47D2-8804-EA03A9B39F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{402FC98C-65C2-4285-BDD0-4C8BB6AD069A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -283,7 +283,7 @@
     <t>Built from capabilities/economic-research/spec.md. Blue = input (all DRAFT placeholders until sourced). Yellow = decision cell (Solver changes these). Black = formula. Money in USD millions ($M).</t>
   </si>
   <si>
-    <t>HOW TO USE: replace blue inputs with sourced figures, pick ACTIVE_RAID and BUDGET, then Data &gt; Solver &gt; Solve (the Solver setup is saved in this sheet). Site constraints (16 sites, Patriot at 2 sites per battery, at most 4 batteries) are in rows 98-141 and the QC grid; QU (rows 35-38) is the grid at sites without Patriot cover.</t>
+    <t>HOW TO USE: replace blue inputs with sourced figures, pick ACTIVE_RAID and BUDGET, then Data &gt; Solver &gt; Solve (the Solver setup is saved in this sheet). Site constraints (16 sites, Patriot at 2 sites per battery, at most 8 batteries) are in rows 98-141 and the QC grid; QU (rows 35-38) is the grid at sites without Patriot cover.</t>
   </si>
   <si>
     <t>INPUTS - per interceptor (DRAFT: secondary-source ranges and placeholder assumptions)</t>
@@ -829,7 +829,7 @@
     <t>batteries</t>
   </si>
   <si>
-    <t>User-specified: the limit on Patriot batteries on Guam.</t>
+    <t>User-specified: 8 Patriot batteries on Guam (the limit; the model may build fewer). At 2 sites each, 8 batteries cover all 16 sites.</t>
   </si>
   <si>
     <t>AEGIS_SITES</t>
@@ -967,16 +967,16 @@
     <t>HAND CHECK - site constraints (build audit): formula vs. hand math</t>
   </si>
   <si>
-    <t>4 batteries x 2 sites = 8 covered sites, half of 16 (COVERED_FRACTION = 0.5)</t>
-  </si>
-  <si>
-    <t>40 ballistic threats, half arriving at covered sites: R_COVERED = 20</t>
-  </si>
-  <si>
-    <t>4 Patriot batteries x 6 launchers x 16 CRI = 384 PAC-3 CRI at most</t>
-  </si>
-  <si>
-    <t>Uncovered share: 8 of 16 sites uncovered, so (1 - 0.5) x 50 drones = 25</t>
+    <t>8 batteries x 2 sites = 16 covered sites = every site (COVERED_FRACTION = 1)</t>
+  </si>
+  <si>
+    <t>40 ballistic threats, all arriving at covered sites: R_COVERED = 40 (R_UNCOVERED = 0)</t>
+  </si>
+  <si>
+    <t>8 Patriot batteries x 6 launchers x 16 CRI = 768 PAC-3 CRI at most</t>
+  </si>
+  <si>
+    <t>With 4 batteries, 8 of 16 sites are uncovered, so (1 - 0.5) x 50 drones = 25 uncovered</t>
   </si>
   <si>
     <t>Raid scenarios and results log</t>
@@ -1033,7 +1033,7 @@
     <t>A ballistic-heavy (USE_MIN 0.98)</t>
   </si>
   <si>
-    <t>Source: scipy.optimize.milp run by Claude on 2026-10-08 with the Model sheet inputs as built, with the site constraints (16 sites, raids spread evenly, 2 sites per Patriot battery, at most 4 batteries, Patriot interceptors only at covered sites); tangent-line approximation of D, protection re-evaluated exactly. These replace the earlier results that had no site limits. Illustrative only.</t>
+    <t>Source: scipy.optimize.milp run by Claude on 2026-10-08 with the Model sheet inputs as built, with the site constraints (16 sites, raids spread evenly, 2 sites per Patriot battery, at most 8 batteries, Patriot interceptors only at covered sites); tangent-line approximation of D, protection re-evaluated exactly. These replace the earlier results that had no site limits. Illustrative only.</t>
   </si>
   <si>
     <t>MY SOLVER RUNS - record each Excel Solver result here</t>
@@ -1153,7 +1153,7 @@
     <t>Constraint 11</t>
   </si>
   <si>
-    <t>PATRIOT_BATTERIES (C41) &lt;= PATRIOT_MAX (B102) - the Guam limit of 4 batteries; 2 sites each, so at most 8 of 16 sites have Patriot cover</t>
+    <t>PATRIOT_BATTERIES (C41) &lt;= PATRIOT_MAX (B102) - the limit of 8 batteries; 2 sites each, so 8 batteries cover all 16 sites</t>
   </si>
   <si>
     <t>Constraint 12</t>
@@ -3768,7 +3768,7 @@
         <v>182</v>
       </c>
       <c r="B102" s="30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -4466,11 +4466,11 @@
         <v>230</v>
       </c>
       <c r="B138" s="27">
-        <f>MIN(16,2*4)/16</f>
-        <v>0.5</v>
+        <f>MIN(16,2*8)/16</f>
+        <v>1</v>
       </c>
       <c r="C138" s="10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2" t="b">
         <f>B138=C138</f>
@@ -4487,11 +4487,11 @@
         <v>231</v>
       </c>
       <c r="B139" s="27">
-        <f>40*(MIN(16,2*4)/16)</f>
-        <v>20</v>
+        <f>40*(MIN(16,2*8)/16)</f>
+        <v>40</v>
       </c>
       <c r="C139" s="10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D139" s="2" t="b">
         <f>B139=C139</f>
@@ -4508,11 +4508,11 @@
         <v>232</v>
       </c>
       <c r="B140" s="27">
-        <f>4*6*16</f>
-        <v>384</v>
+        <f>8*6*16</f>
+        <v>768</v>
       </c>
       <c r="C140" s="10">
-        <v>384</v>
+        <v>768</v>
       </c>
       <c r="D140" s="2" t="b">
         <f>B140=C140</f>

--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -8,21 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richi\AppData\Local\Temp\mx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{402FC98C-65C2-4285-BDD0-4C8BB6AD069A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18976A0C-88FC-4CDF-883A-7A9AE54E329A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="2" r:id="rId2"/>
-    <sheet name="Solver Model" sheetId="3" r:id="rId3"/>
+    <sheet name="Table 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId3"/>
+    <sheet name="Solver Model" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ACTIVE_RAID">Model!$B$31</definedName>
+    <definedName name="AEGIS_ALLOWED">Model!$B$166</definedName>
     <definedName name="AEGIS_CELL_SLACK">Model!$B$61</definedName>
     <definedName name="AEGIS_CELLS_USED">Model!$B$60</definedName>
     <definedName name="AEGIS_SITES">Model!$B$103</definedName>
     <definedName name="ALL_VALID">Model!$B$89</definedName>
+    <definedName name="ALLOWED">Model!$B$157:$G$159</definedName>
+    <definedName name="ALLOWED_NOW">Model!$B$160:$G$160</definedName>
     <definedName name="BUDGET">Model!$B$23</definedName>
     <definedName name="BUILD_AEGIS">Model!$B$41</definedName>
     <definedName name="BUILD_THAAD">Model!$D$41</definedName>
@@ -36,9 +40,11 @@
     <definedName name="EFF_UNCOVERED">Model!$B$124:$E$124</definedName>
     <definedName name="FLOOR">Model!$B$18:$E$18</definedName>
     <definedName name="INTERCEPTOR_SPEND">Model!$B$55</definedName>
+    <definedName name="KRATE">Model!$B$147:$G$150</definedName>
     <definedName name="MIN_REQUIRED">Model!$B$52:$E$52</definedName>
     <definedName name="MK41_CELLS">Model!$B$28</definedName>
     <definedName name="MSE_CAP">Model!$C$13</definedName>
+    <definedName name="MSE_FULL_SLACK">Model!$B$167</definedName>
     <definedName name="MSE_PK_ABT">Model!$C$11</definedName>
     <definedName name="MSE_PK_BM">Model!$C$9</definedName>
     <definedName name="MSE_PK_CM">Model!$C$10</definedName>
@@ -46,6 +52,7 @@
     <definedName name="MSE_PRICE">Model!$C$7</definedName>
     <definedName name="MSE_Q">Model!$C$45</definedName>
     <definedName name="MSE_SYSTEM">Model!$C$8</definedName>
+    <definedName name="OPTION">Model!$B$154</definedName>
     <definedName name="PAC3_CAP">Model!$B$13</definedName>
     <definedName name="PAC3_PK_ABT">Model!$B$11</definedName>
     <definedName name="PAC3_PK_BM">Model!$B$9</definedName>
@@ -58,6 +65,8 @@
     <definedName name="PATRIOT_LAUNCHERS">Model!$B$29</definedName>
     <definedName name="PATRIOT_LAUNCHERS_USED">Model!$B$62</definedName>
     <definedName name="PATRIOT_MAX">Model!$B$102</definedName>
+    <definedName name="PATRIOT_MAX_NOW">Model!$B$165</definedName>
+    <definedName name="PATRIOT_MIN">Model!$B$164</definedName>
     <definedName name="PATRIOT_SITES_COVERED">Model!$B$115</definedName>
     <definedName name="PATRIOT_SLACK">Model!$B$63</definedName>
     <definedName name="PK_ABT">Model!$B$11:$G$11</definedName>
@@ -118,7 +127,10 @@
     <definedName name="solver_lhs15" localSheetId="0">Model!$C$41</definedName>
     <definedName name="solver_lhs16" localSheetId="0">Model!$B$35:$C$38</definedName>
     <definedName name="solver_lhs17" localSheetId="0">Model!$B$118</definedName>
+    <definedName name="solver_lhs18" localSheetId="0">Model!$C$41</definedName>
+    <definedName name="solver_lhs19" localSheetId="0">Model!$B$41</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">Model!$B$35:$G$38</definedName>
+    <definedName name="solver_lhs20" localSheetId="0">Model!$B$167</definedName>
     <definedName name="solver_lhs3" localSheetId="0">Model!$B$41</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">Model!$B$57</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">Model!$B$57</definedName>
@@ -131,7 +143,7 @@
     <definedName name="solver_msl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="0">17</definedName>
+    <definedName name="solver_num" localSheetId="0">20</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">Model!$B$65</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
@@ -144,7 +156,10 @@
     <definedName name="solver_rel15" localSheetId="0">1</definedName>
     <definedName name="solver_rel16" localSheetId="0">2</definedName>
     <definedName name="solver_rel17" localSheetId="0">3</definedName>
+    <definedName name="solver_rel18" localSheetId="0">3</definedName>
+    <definedName name="solver_rel19" localSheetId="0">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel20" localSheetId="0">2</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">5</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">3</definedName>
@@ -158,10 +173,13 @@
     <definedName name="solver_rhs12" localSheetId="0">0</definedName>
     <definedName name="solver_rhs13" localSheetId="0">"integer"</definedName>
     <definedName name="solver_rhs14" localSheetId="0">0</definedName>
-    <definedName name="solver_rhs15" localSheetId="0">Model!$B$102</definedName>
+    <definedName name="solver_rhs15" localSheetId="0">Model!$B$165</definedName>
     <definedName name="solver_rhs16" localSheetId="0">0</definedName>
     <definedName name="solver_rhs17" localSheetId="0">0</definedName>
+    <definedName name="solver_rhs18" localSheetId="0">Model!$B$164</definedName>
+    <definedName name="solver_rhs19" localSheetId="0">Model!$B$166</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rhs20" localSheetId="0">0</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">"binary"</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">Model!$B$23</definedName>
     <definedName name="solver_rhs5" localSheetId="0" hidden="1">Model!$B$58</definedName>
@@ -225,6 +243,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Claude Code</author>
     <author>Unknown Author</author>
   </authors>
   <commentList>
@@ -238,7 +257,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>Draft range $3-4M (Norsk Luftvern). Verify: Army missile procurement justification book.</t>
+          <t>Table 1: $3.7M (CRI is not confirmed for Guam). Not confirmed against a primary source.</t>
         </r>
       </text>
     </comment>
@@ -252,11 +271,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>Draft range $28-36M for SM-3 Block IIA; Block IB is $12-15M. Choose the variant Guam will field.</t>
+          <t>Table 1: $27.9M for SM-3 IIA. Reported estimates range from about $28M to $31M; not confirmed to a budget book.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D41" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -275,15 +294,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="297">
-  <si>
-    <t>Guam interceptor loadout - economic research model (ILLUSTRATIVE build 2026-10-02; site constraints added 2026-10-08)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="375">
+  <si>
+    <t>Guam interceptor loadout - economic research model (inputs from Table 1 of the paper, 2026-10-10; site constraints, kill rate and options added)</t>
   </si>
   <si>
     <t>Built from capabilities/economic-research/spec.md. Blue = input (all DRAFT placeholders until sourced). Yellow = decision cell (Solver changes these). Black = formula. Money in USD millions ($M).</t>
   </si>
   <si>
-    <t>HOW TO USE: replace blue inputs with sourced figures, pick ACTIVE_RAID and BUDGET, then Data &gt; Solver &gt; Solve (the Solver setup is saved in this sheet). Site constraints (16 sites, Patriot at 2 sites per battery, at most 8 batteries) are in rows 98-141 and the QC grid; QU (rows 35-38) is the grid at sites without Patriot cover.</t>
+    <t>HOW TO USE: set OPTION, ACTIVE_RAID and BUDGET, then Data &gt; Solver &gt; Solve (the Solver setup is saved in this sheet). Inputs are from Table 1 of the paper; kill probabilities, raid sizes, weights and the even spread over 16 sites are placeholders. Site constraints are in rows 98-143; options in rows 152-175.</t>
   </si>
   <si>
     <t>INPUTS - per interceptor (DRAFT: secondary-source ranges and placeholder assumptions)</t>
@@ -322,7 +341,7 @@
     <t>$M per interceptor</t>
   </si>
   <si>
-    <t>Draft midpoints: Norsk Luftvern cost database (PAC-3, MSE, THAAD, SM-3 IIA); CSIS Feb 2024 (SM-2 ~ $2M); Wikipedia RIM-174 FY2021 avg (SM-6). Replace with budget-book unit costs.</t>
+    <t>Table 1 (paper, 2026-10-09): CRI $3.7M, MSE $4.2M, THAAD $12.7M, SM-3 IIA $27.9M, SM-2 $2.0-2.1M and SM-6 $3.5-9.6M (midpoints used for the two ranges). NOT yet confirmed against budget books or contract awards; see the paper's price notes.</t>
   </si>
   <si>
     <t>SYSTEM</t>
@@ -346,34 +365,28 @@
     <t>single-shot kill prob.</t>
   </si>
   <si>
-    <t>PLACEHOLDER assumption (classified values out of scope). 0 = cannot engage.</t>
+    <t>Single-shot kill probability: 50% baseline (PLACEHOLDER) wherever Table 1 lists the threat for that interceptor; 0 = cannot engage. n shots at one threat kill it with probability 1 - (1 - PK)^n (see KRATE). Row BM.</t>
   </si>
   <si>
     <t>PK_CM</t>
   </si>
   <si>
-    <t>PLACEHOLDER assumption. ARM (anti-radiation missiles) folded into CM.</t>
+    <t>Single-shot kill probability: 50% baseline (PLACEHOLDER) wherever Table 1 lists the threat for that interceptor; 0 = cannot engage. n shots at one threat kill it with probability 1 - (1 - PK)^n (see KRATE).</t>
   </si>
   <si>
     <t>PK_ABT</t>
   </si>
   <si>
-    <t>PLACEHOLDER assumption. RW (helicopters) folded into ABT.</t>
-  </si>
-  <si>
     <t>PK_UAS</t>
   </si>
   <si>
-    <t>PLACEHOLDER assumption.</t>
-  </si>
-  <si>
     <t>CAP</t>
   </si>
   <si>
     <t>interceptors through FY2032</t>
   </si>
   <si>
-    <t>PLACEHOLDER (set non-binding). Replace with production rate x years.</t>
+    <t>PLACEHOLDER (non-binding): no Table 2 result buys more than 615 of one type. Replace with production rate x years.</t>
   </si>
   <si>
     <t>INPUTS - per threat class</t>
@@ -430,7 +443,7 @@
     <t>$M</t>
   </si>
   <si>
-    <t>PLACEHOLDER. Interceptor + launcher-system share of the ~$8B Guam program (Arms Control Assn, Oct 2025) is not yet sourced. Pull from MDA budget books.</t>
+    <t>The roughly $8B Guam Defense System cap (Arms Control Association, 2025), used as the interceptor and system budget. PLACEHOLDER: the interceptor share is not sourced.</t>
   </si>
   <si>
     <t>USE_MIN</t>
@@ -448,7 +461,7 @@
     <t>$M, one system</t>
   </si>
   <si>
-    <t>Draft: ~$1.9B reported for Aegis Guam (Army Recognition 2026). Verify against MDA books.</t>
+    <t>Table 1: Aegis Guam $1.9B (Brahy, 2026). Note: one report describes $1.9B as the cumulative value of a broader Aegis contract, not a Guam-only cost.</t>
   </si>
   <si>
     <t>SYS_COST_PATRIOT</t>
@@ -457,7 +470,7 @@
     <t>$M, one battery</t>
   </si>
   <si>
-    <t>Draft: ~$1.09B per battery, FY2022 (Wikipedia, MIM-104 Patriot).</t>
+    <t>Table 1: Patriot battery about $0.4B without missiles. Supported by a secondary source citing CRS; not confirmed to a budget book. Counted once per battery.</t>
   </si>
   <si>
     <t>SYS_COST_THAAD</t>
@@ -472,7 +485,7 @@
     <t>launcher cells</t>
   </si>
   <si>
-    <t>PLACEHOLDER. Aegis Guam Mk 41 cell count not yet sourced. Shared by SM-2, SM-3, SM-6.</t>
+    <t>PLACEHOLDER (Table 1 dagger). Aegis Guam Mk 41 cell count not yet sourced. Shared by SM-2, SM-3, SM-6.</t>
   </si>
   <si>
     <t>PATRIOT_LAUNCHERS</t>
@@ -571,7 +584,7 @@
     <t>expected kills if unsaturated</t>
   </si>
   <si>
-    <t>EFF_j = EFF_COVERED_j + EFF_UNCOVERED_j</t>
+    <t>EFF_j = EFF_COVERED_j + EFF_UNCOVERED_j; each is SUM of KRATE x Q</t>
   </si>
   <si>
     <t>D (defeated)</t>
@@ -673,7 +686,7 @@
     <t>CAP_SLACK</t>
   </si>
   <si>
-    <t>CAP_i - Q_i  (Solver: &gt;= 0)</t>
+    <t>CAP_i x ALLOWED_NOW_i - Q_i  (Solver: &gt;= 0; a type the option does not allow gets a cap of 0)</t>
   </si>
   <si>
     <t>EQUIMARGINAL CHECK - extra weighted protection from ONE more interceptor, per $M (build audit)</t>
@@ -691,7 +704,7 @@
     <t>weighted threats per $M</t>
   </si>
   <si>
-    <t>W_j x [extra threats defeated at the best site type by one more shot] / PRICE_i  (Patriot: covered sites only)</t>
+    <t>W_j x [extra threats defeated at the best site type by one more interceptor] / PRICE_i  (Patriot: covered sites only)</t>
   </si>
   <si>
     <t>MPD_CM</t>
@@ -790,10 +803,10 @@
     <t>Match?</t>
   </si>
   <si>
-    <t>20 threats, 10 shots at PK 0.7 (EFF = 7): D = 20 x (1 - e^-0.35) = 5.906</t>
-  </si>
-  <si>
-    <t>Adding one more PK-0.7 shot (EFF 7.7) raises D to 6.391</t>
+    <t>20 threats, effective shots EFF = 7: D = 20 x (1 - e^-0.35) = 5.906</t>
+  </si>
+  <si>
+    <t>Adding 0.7 effective shots (EFF 7.7) raises D to 6.391</t>
   </si>
   <si>
     <t>Patriot: 96 CRI fill exactly 6 launchers (96/16)</t>
@@ -910,13 +923,13 @@
     <t>EFF_COVERED</t>
   </si>
   <si>
-    <t>SUMPRODUCT(PK_j, QC_j)</t>
+    <t>SUMPRODUCT(KRATE_j, QC_j)</t>
   </si>
   <si>
     <t>EFF_UNCOVERED</t>
   </si>
   <si>
-    <t>SUMPRODUCT(PK_j, QU_j)</t>
+    <t>SUMPRODUCT(KRATE_j, QU_j)</t>
   </si>
   <si>
     <t>D_COVERED</t>
@@ -979,6 +992,237 @@
     <t>With 4 batteries, 8 of 16 sites are uncovered, so (1 - 0.5) x 50 drones = 25 uncovered</t>
   </si>
   <si>
+    <t>Two shots at PK 0.5 against one threat kill it with probability 0.75: 1 x (1 - e^(-KRATE x 2))</t>
+  </si>
+  <si>
+    <t>One shot per threat at PK 0.5 defeats half: 20 threats, 20 shots, D = 10</t>
+  </si>
+  <si>
+    <t>CALCULATIONS - kill rate from single-shot kill probability (salvo form)</t>
+  </si>
+  <si>
+    <t>KRATE_BM</t>
+  </si>
+  <si>
+    <t>effective shots per interceptor</t>
+  </si>
+  <si>
+    <t>KRATE = -LN(1 - PK). One interceptor adds KRATE effective shots; D = R x (1 - EXP(-EFF / R)) then gives 1 - (1 - PK)^n for n interceptors per threat</t>
+  </si>
+  <si>
+    <t>KRATE_CM</t>
+  </si>
+  <si>
+    <t>KRATE_ABT</t>
+  </si>
+  <si>
+    <t>KRATE_UAS</t>
+  </si>
+  <si>
+    <t>INPUTS - which Table 2 option to run (OPTION 1, 2 or 3)</t>
+  </si>
+  <si>
+    <t>OPTION</t>
+  </si>
+  <si>
+    <t>1, 2 or 3</t>
+  </si>
+  <si>
+    <t>1 = 8 Patriot batteries with MSE only; 2 = current Guam plan (Aegis + existing THAAD); 3 = optimal mix. Choose, then run Solver (see the Solver Model sheet).</t>
+  </si>
+  <si>
+    <t>ALLOWED (1 = may buy)</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>ALLOWED_OPTION_1</t>
+  </si>
+  <si>
+    <t>0 or 1</t>
+  </si>
+  <si>
+    <t>Option 1: only PAC-3 MSE, on Patriot batteries (no Aegis, no THAAD interceptors)</t>
+  </si>
+  <si>
+    <t>ALLOWED_OPTION_2</t>
+  </si>
+  <si>
+    <t>Option 2: the current Guam plan: Aegis (SM-3 IIA, SM-6) plus the existing, already-paid THAAD battery; no Patriot, no SM-2</t>
+  </si>
+  <si>
+    <t>ALLOWED_OPTION_3</t>
+  </si>
+  <si>
+    <t>Option 3: every interceptor type may be bought</t>
+  </si>
+  <si>
+    <t>ALLOWED_NOW</t>
+  </si>
+  <si>
+    <t>ALLOWED row for the active OPTION; production cap becomes CAP x ALLOWED_NOW</t>
+  </si>
+  <si>
+    <t>CALCULATIONS - option rules</t>
+  </si>
+  <si>
+    <t>PATRIOT_MIN</t>
+  </si>
+  <si>
+    <t>Option 1 builds all PATRIOT_MAX batteries</t>
+  </si>
+  <si>
+    <t>PATRIOT_MAX_NOW</t>
+  </si>
+  <si>
+    <t>Option 2 has no Patriot batteries</t>
+  </si>
+  <si>
+    <t>AEGIS_ALLOWED</t>
+  </si>
+  <si>
+    <t>Option 1 has no Aegis system</t>
+  </si>
+  <si>
+    <t>MSE_FULL_SLACK</t>
+  </si>
+  <si>
+    <t>Option 1 loads every battery fully with MSE (12 per launcher); Solver: = 0</t>
+  </si>
+  <si>
+    <t>VALIDATION RULES - option; each TRUE/FALSE; rolled up into ALL_VALID</t>
+  </si>
+  <si>
+    <t>Only allowed interceptor types are bought</t>
+  </si>
+  <si>
+    <t>buying a type the active OPTION does not allow</t>
+  </si>
+  <si>
+    <t>Patriot batteries match the option</t>
+  </si>
+  <si>
+    <t>Option 1 below PATRIOT_MAX batteries, or Patriot batteries in Option 2</t>
+  </si>
+  <si>
+    <t>Aegis system only if the option allows it</t>
+  </si>
+  <si>
+    <t>an Aegis system in Option 1</t>
+  </si>
+  <si>
+    <t>Option 1 batteries fully loaded with MSE</t>
+  </si>
+  <si>
+    <t>Option 1 with empty launchers</t>
+  </si>
+  <si>
+    <t>Table 2 of the paper: where each number comes from</t>
+  </si>
+  <si>
+    <t>Each Table 2 cell is the PROTECTION cell (Model!B65) after setting OPTION (Model!B154), ACTIVE_RAID (Model!B31) and BUDGET (Model!B23 = 8,000) and solving. The reference values on the Scenarios sheet (rows 13-21) come from an external integer solver (reference-optimizer.py, in this folder); column E checks each of the paper's rounded values against them (FALSE = the paper's number differs from the workbook).</t>
+  </si>
+  <si>
+    <t>Inputs are Table 1 of the paper; the 50% kill probability, raid sizes, damage weights and the even spread of threats over 16 sites are placeholders. Options 2 and 3 are re-solved for each raid; Option 1 is one fixed purchase.</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>Raid</t>
+  </si>
+  <si>
+    <t>Paper Table 2 (%)</t>
+  </si>
+  <si>
+    <t>Workbook reference (%)</t>
+  </si>
+  <si>
+    <t>Matches paper?</t>
+  </si>
+  <si>
+    <t>Spend ($M)</t>
+  </si>
+  <si>
+    <t>Protection points per $B</t>
+  </si>
+  <si>
+    <t>How to reproduce</t>
+  </si>
+  <si>
+    <t>OPTION = 1, ACTIVE_RAID = A ballistic-heavy, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 1, ACTIVE_RAID = B cruise-heavy, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 1, ACTIVE_RAID = C drone saturation, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 2, ACTIVE_RAID = A ballistic-heavy, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 2, ACTIVE_RAID = B cruise-heavy, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 2, ACTIVE_RAID = C drone saturation, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 3, ACTIVE_RAID = A ballistic-heavy, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 3, ACTIVE_RAID = B cruise-heavy, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>OPTION = 3, ACTIVE_RAID = C drone saturation, BUDGET = 8000, USE_MIN = 0; solve; read Model!B65</t>
+  </si>
+  <si>
+    <t>ALL NINE MATCH</t>
+  </si>
+  <si>
+    <t>Table 2 spend column</t>
+  </si>
+  <si>
+    <t>Paper low ($B)</t>
+  </si>
+  <si>
+    <t>Paper high ($B)</t>
+  </si>
+  <si>
+    <t>Workbook low ($B)</t>
+  </si>
+  <si>
+    <t>Workbook high ($B)</t>
+  </si>
+  <si>
+    <t>MOST BANG FOR THE BUCK: best protection (Option 3, unrestricted) at each budget, per raid</t>
+  </si>
+  <si>
+    <t>Hardcoded values from the same external solver (reference-optimizer.py), not Excel Solver. Protection points per $B = protection (%) / spend ($B). Extra points per extra $B = change from the previous budget for the same raid. Compare Options 1 and 2 above (points per $B in column G).</t>
+  </si>
+  <si>
+    <t>Budget ($M)</t>
+  </si>
+  <si>
+    <t>Protection (%)</t>
+  </si>
+  <si>
+    <t>Extra points per extra $B</t>
+  </si>
+  <si>
+    <t>Patriot batteries</t>
+  </si>
+  <si>
+    <t>Aegis built</t>
+  </si>
+  <si>
+    <t>B cruise-heavy</t>
+  </si>
+  <si>
+    <t>C drone saturation</t>
+  </si>
+  <si>
     <t>Raid scenarios and results log</t>
   </si>
   <si>
@@ -994,25 +1238,16 @@
     <t>mostly medium/intermediate-range ballistic missiles</t>
   </si>
   <si>
-    <t>B cruise-heavy</t>
-  </si>
-  <si>
     <t>mostly cruise missiles and aircraft</t>
   </si>
   <si>
-    <t>C drone saturation</t>
-  </si>
-  <si>
     <t>mostly cheap one-way attack drones</t>
   </si>
   <si>
-    <t>REFERENCE RESULTS - independent check (Python integer optimizer, same illustrative inputs, WITH the site constraints, USE_MIN = 0 unless noted)</t>
-  </si>
-  <si>
-    <t>Hardcoded values from an external solver, for checking Excel Solver only. Solver should reach the same PROTECTION within ~0.5 points; if it is lower, re-solve from a different starting point (GRG can stop at a local optimum).</t>
-  </si>
-  <si>
-    <t>Budget ($M)</t>
+    <t>REFERENCE RESULTS - the nine Table 2 cells (Python integer optimizer, same inputs, OPTION x raid, BUDGET = 8,000, USE_MIN = 0)</t>
+  </si>
+  <si>
+    <t>Hardcoded values from an external solver, for checking Excel Solver only. Set OPTION and ACTIVE_RAID, then solve. Solver should reach the same PROTECTION within ~0.5 points; different mixes can tie, so compare PROTECTION and spend, not exact quantities.</t>
   </si>
   <si>
     <t>Protection</t>
@@ -1021,19 +1256,19 @@
     <t>Spent ($M)</t>
   </si>
   <si>
-    <t>Aegis built</t>
-  </si>
-  <si>
-    <t>Patriot batteries</t>
-  </si>
-  <si>
     <t>Patriot sites</t>
   </si>
   <si>
-    <t>A ballistic-heavy (USE_MIN 0.98)</t>
-  </si>
-  <si>
-    <t>Source: scipy.optimize.milp run by Claude on 2026-10-08 with the Model sheet inputs as built, with the site constraints (16 sites, raids spread evenly, 2 sites per Patriot battery, at most 8 batteries, Patriot interceptors only at covered sites); tangent-line approximation of D, protection re-evaluated exactly. These replace the earlier results that had no site limits. Illustrative only.</t>
+    <t>1 - 8 Patriot batteries, MSE only</t>
+  </si>
+  <si>
+    <t>2 - current Guam plan</t>
+  </si>
+  <si>
+    <t>3 - optimal mix (up to 8 batteries)</t>
+  </si>
+  <si>
+    <t>Source: scipy.optimize.milp run by Claude on 2026-10-10 with the Model sheet inputs as built (Table 1 prices, 50% single-shot kill probability in the salvo form, 16 sites, up to 8 Patriot batteries at 2 sites each); tangent-line approximation of D, protection re-evaluated exactly. These are the nine cells of Table 2 in the paper (92 / 89 / 49, 68 / 53 / 43, 97 / 95 / 59 percent). Illustrative only.</t>
   </si>
   <si>
     <t>MY SOLVER RUNS - record each Excel Solver result here</t>
@@ -1057,13 +1292,13 @@
     <t>By changing</t>
   </si>
   <si>
-    <t>QU grid Model!B35:G38 (interceptors at sites without Patriot cover), QC grid Model!B108:G111 (interceptors at Patriot-covered sites), BUILD_AEGIS Model!B41 (buy Aegis Guam) and PATRIOT_BATTERIES Model!C41 (number of Patriot batteries, 0 to PATRIOT_MAX). THAAD build is fixed at 1: the battery is already on Guam.</t>
+    <t>QU grid Model!B35:G38 and QC grid Model!B108:G111 (interceptors at uncovered / Patriot-covered sites), BUILD_AEGIS Model!B41 and PATRIOT_BATTERIES Model!C41 (number of Patriot batteries). THAAD build is fixed at 1: the battery is already on Guam. Set OPTION (Model!B154) first.</t>
   </si>
   <si>
     <t>Engine</t>
   </si>
   <si>
-    <t>GRG Nonlinear (the objective uses EXP, so Simplex LP cannot be used), with Multistart on. Integer optimality tolerance 0%.</t>
+    <t>GRG Nonlinear (the objective uses EXP, so Simplex LP cannot be used), with Multistart on. Integer optimality tolerance 0%. Not run in the build (Solver hangs headless).</t>
   </si>
   <si>
     <t>Constraint 1</t>
@@ -1087,7 +1322,7 @@
     <t>Constraint 4</t>
   </si>
   <si>
-    <t>TOTAL_SPEND (B57) &lt;= BUDGET (B23)</t>
+    <t>TOTAL_SPEND (B57) &lt;= BUDGET (B23); BUDGET = 8,000 for Table 2</t>
   </si>
   <si>
     <t>Constraint 5</t>
@@ -1117,7 +1352,7 @@
     <t>Constraint 9</t>
   </si>
   <si>
-    <t>CAP_SLACK (B67:G67) &gt;= 0  - production through FY2032</t>
+    <t>CAP_SLACK (B67:G67) &gt;= 0  - production cap CAP x ALLOWED_NOW, so a type the OPTION does not allow cannot be bought</t>
   </si>
   <si>
     <t>Constraint 10</t>
@@ -1129,19 +1364,19 @@
     <t>Build audit</t>
   </si>
   <si>
-    <t>1) Hand check rows (Model, rows 93-96 and 138-141) all TRUE.  2) ALL_VALID (B89) TRUE after every solve.  3) Solve from two starting points (the seeded solution, and all zeros) and compare.  4) Compare PROTECTION with the reference results on the Scenarios sheet.  5) Equimarginal check: interceptors in use should show similar MPD values (rows 71-74) unless a cell, launcher or site limit binds.</t>
+    <t>1) Hand check rows (Model, rows 93-96, 138-143) all TRUE.  2) ALL_VALID (B89) TRUE after every solve.  3) Solve from two starting points (the seeded solution, and all zeros) and compare.  4) Compare PROTECTION with the reference results on the Scenarios sheet.  5) Equimarginal check: interceptors in use should show similar MPD values (rows 71-74) unless a cell, launcher or site limit binds.</t>
   </si>
   <si>
     <t>Starting point</t>
   </si>
   <si>
-    <t>The decision cells are seeded with the reference solution for scenario A at $4,000M, so the sheet opens in a solved state.</t>
+    <t>The decision cells are seeded with the reference solution for OPTION 3 (optimal mix), raid A, at $8,000M, so the sheet opens in a solved state.</t>
   </si>
   <si>
     <t>Run plan (spec)</t>
   </si>
   <si>
-    <t>For each scenario A, B, C: solve at BUDGET = 2,000 / 4,000 / 6,000 with USE_MIN = 0; then the "use the whole budget" run with USE_MIN = 0.98; record results on the Scenarios sheet.</t>
+    <t>For each OPTION 1, 2, 3 and each raid A, B, C: solve at BUDGET = 8,000 with USE_MIN = 0 and compare with the Scenarios sheet (these are the cells of Table 2 in the paper).</t>
   </si>
   <si>
     <t>Known limits</t>
@@ -1153,7 +1388,7 @@
     <t>Constraint 11</t>
   </si>
   <si>
-    <t>PATRIOT_BATTERIES (C41) &lt;= PATRIOT_MAX (B102) - the limit of 8 batteries; 2 sites each, so 8 batteries cover all 16 sites</t>
+    <t>PATRIOT_BATTERIES (C41) &lt;= PATRIOT_MAX_NOW (the limit of 8; 0 in Option 2); 2 sites each, so 8 batteries cover all 16 sites</t>
   </si>
   <si>
     <t>Constraint 12</t>
@@ -1166,6 +1401,24 @@
   </si>
   <si>
     <t>QC_SLACK (B118) &gt;= 0 - nothing at covered sites when no site is covered</t>
+  </si>
+  <si>
+    <t>Constraint 14</t>
+  </si>
+  <si>
+    <t>PATRIOT_BATTERIES (C41) &gt;= PATRIOT_MIN (B164) - Option 1 builds all 8 batteries</t>
+  </si>
+  <si>
+    <t>Constraint 15</t>
+  </si>
+  <si>
+    <t>BUILD_AEGIS (B41) &lt;= AEGIS_ALLOWED (B166) - no Aegis system in Option 1</t>
+  </si>
+  <si>
+    <t>Constraint 16</t>
+  </si>
+  <si>
+    <t>MSE_FULL_SLACK (B167) = 0 - Option 1 loads every battery fully with MSE</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1433,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,8 +1489,34 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1274,6 +1553,16 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1287,7 +1576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1322,6 +1611,22 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1586,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1698,22 +2003,22 @@
         <v>13</v>
       </c>
       <c r="B7" s="8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="C7" s="8">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="D7" s="8">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="E7" s="8">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="F7" s="8">
-        <v>2</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="G7" s="8">
-        <v>4.3</v>
+        <v>6.55</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>14</v>
@@ -1758,22 +2063,22 @@
         <v>21</v>
       </c>
       <c r="B9" s="11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
       </c>
       <c r="G9" s="11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>22</v>
@@ -1788,10 +2093,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="11">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="11">
         <v>0</v>
@@ -1800,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>22</v>
@@ -1818,10 +2123,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="11">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C11" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="11">
         <v>0</v>
@@ -1830,25 +2135,25 @@
         <v>0</v>
       </c>
       <c r="F11" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="11">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="11">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="C12" s="11">
         <v>0</v>
@@ -1860,46 +2165,46 @@
         <v>0</v>
       </c>
       <c r="F12" s="11">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="G12" s="11">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="E13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="G13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="10">
-        <v>500</v>
-      </c>
-      <c r="C13" s="10">
-        <v>500</v>
-      </c>
-      <c r="D13" s="10">
-        <v>500</v>
-      </c>
-      <c r="E13" s="10">
-        <v>500</v>
-      </c>
-      <c r="F13" s="10">
-        <v>500</v>
-      </c>
-      <c r="G13" s="10">
-        <v>500</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="J13" s="2"/>
     </row>
@@ -1917,7 +2222,7 @@
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1934,16 +2239,16 @@
         <v>4</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1957,7 +2262,7 @@
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" s="10">
         <v>10</v>
@@ -1974,16 +2279,16 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="12">
         <v>0</v>
@@ -2000,16 +2305,16 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19" s="13">
         <f>INDEX(Scenarios!B$5:B$7,MATCH(ACTIVE_RAID,Scenarios!$A$5:$A$7,0))</f>
@@ -2030,10 +2335,10 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -2051,7 +2356,7 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2068,7 +2373,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -2085,10 +2390,10 @@
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="14">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2096,16 +2401,16 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="15">
         <v>0</v>
@@ -2116,16 +2421,16 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="16">
         <v>1900</v>
@@ -2136,19 +2441,19 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="16">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -2156,16 +2461,16 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" s="16">
         <v>0</v>
@@ -2176,16 +2481,16 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B28" s="17">
         <v>96</v>
@@ -2196,16 +2501,16 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B29" s="17">
         <v>6</v>
@@ -2216,16 +2521,16 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" s="17">
         <v>48</v>
@@ -2236,19 +2541,19 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -2256,10 +2561,10 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J31" s="2"/>
     </row>
@@ -2277,7 +2582,7 @@
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2291,7 +2596,7 @@
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>5</v>
@@ -2315,13 +2620,13 @@
         <v>11</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" s="19">
         <v>0</v>
@@ -2330,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="19">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E35" s="19">
         <v>0</v>
@@ -2339,19 +2644,19 @@
         <v>0</v>
       </c>
       <c r="G35" s="19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B36" s="19">
         <v>0</v>
@@ -2366,22 +2671,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G36" s="19">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B37" s="19">
         <v>0</v>
@@ -2396,22 +2701,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G37" s="19">
         <v>0</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" s="19">
         <v>0</v>
@@ -2432,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J38" s="2"/>
     </row>
@@ -2453,13 +2758,13 @@
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>7</v>
@@ -2471,19 +2776,19 @@
         <v>11</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B41" s="20">
         <v>1</v>
       </c>
       <c r="C41" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D41" s="10">
         <v>1</v>
@@ -2492,10 +2797,10 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J41" s="2"/>
     </row>
@@ -2513,7 +2818,7 @@
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2551,25 +2856,25 @@
         <v>11</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J44" s="2"/>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B45" s="21">
         <f t="shared" ref="B45:G45" si="0">SUM(B35:B38)+SUM(B108:B111)</f>
-        <v>42</v>
+        <v>322</v>
       </c>
       <c r="C45" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="D45" s="21">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E45" s="21">
         <f t="shared" si="0"/>
@@ -2577,35 +2882,35 @@
       </c>
       <c r="F45" s="21">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G45" s="21">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J45" s="2"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B46" s="22">
         <f t="shared" ref="B46:G46" si="1">B7*B45</f>
-        <v>147</v>
+        <v>1191.4000000000001</v>
       </c>
       <c r="C46" s="22">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1079.4000000000001</v>
       </c>
       <c r="D46" s="22">
         <f t="shared" si="1"/>
-        <v>580.5</v>
+        <v>0</v>
       </c>
       <c r="E46" s="22">
         <f t="shared" si="1"/>
@@ -2613,17 +2918,17 @@
       </c>
       <c r="F46" s="22">
         <f t="shared" si="1"/>
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="G46" s="22">
         <f t="shared" si="1"/>
-        <v>150.5</v>
+        <v>628.79999999999995</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J46" s="2"/>
     </row>
@@ -2644,125 +2949,125 @@
         <v>4</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F48" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J48" s="2"/>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B49" s="23">
         <f>B123+B124</f>
-        <v>68.599999999999994</v>
+        <v>200.31953518182419</v>
       </c>
       <c r="C49" s="23">
         <f>C123+C124</f>
-        <v>44.4</v>
+        <v>150.41293818150814</v>
       </c>
       <c r="D49" s="23">
         <f>D123+D124</f>
-        <v>12.65</v>
+        <v>50.599744180876009</v>
       </c>
       <c r="E49" s="23">
         <f>E123+E124</f>
-        <v>4.25</v>
+        <v>66.542129333754744</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J49" s="2"/>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B50" s="23">
         <f>B125+B126</f>
-        <v>32.454633327857422</v>
+        <v>39.732626554474187</v>
       </c>
       <c r="C50" s="23">
         <f>C125+C126</f>
-        <v>22.939995128103611</v>
+        <v>29.800624884152146</v>
       </c>
       <c r="D50" s="23">
         <f>D125+D126</f>
-        <v>7.1276348457833167</v>
+        <v>9.9365427815346692</v>
       </c>
       <c r="E50" s="23">
         <f>E125+E126</f>
-        <v>3.0836437977150655</v>
+        <v>36.787274492982746</v>
       </c>
       <c r="F50" s="23">
         <f>SUM(B50:E50)</f>
-        <v>65.605907099459415</v>
+        <v>116.25706871314375</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J50" s="2"/>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B51" s="24">
         <f>IF(B19=0,0,B50/B19)</f>
-        <v>0.81136583319643552</v>
+        <v>0.99331566386185466</v>
       </c>
       <c r="C51" s="24">
         <f>IF(C19=0,0,C50/C19)</f>
-        <v>0.7646665042701204</v>
+        <v>0.99335416280507149</v>
       </c>
       <c r="D51" s="24">
         <f>IF(D19=0,0,D50/D19)</f>
-        <v>0.71276348457833172</v>
+        <v>0.99365427815346696</v>
       </c>
       <c r="E51" s="24">
         <f>IF(E19=0,0,E50/E19)</f>
-        <v>6.1672875954301307E-2</v>
+        <v>0.73574548985965493</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B52" s="23">
         <f>B18*B19</f>
@@ -2783,10 +3088,10 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J52" s="2"/>
     </row>
@@ -2807,7 +3112,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -2818,17 +3123,17 @@
         <v>11</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J54" s="2"/>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B55" s="22">
         <f>SUMPRODUCT(PRICE,Q_TOTAL)</f>
-        <v>1000</v>
+        <v>2899.6000000000004</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -2836,20 +3141,20 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J55" s="2"/>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B56" s="22">
         <f>SYS_COST_AEGIS*BUILD_AEGIS+SYS_COST_PATRIOT*PATRIOT_BATTERIES+SYS_COST_THAAD*BUILD_THAAD</f>
-        <v>3000</v>
+        <v>5100</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -2857,20 +3162,20 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J56" s="2"/>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B57" s="22">
         <f>INTERCEPTOR_SPEND+SYSTEM_SPEND</f>
-        <v>4000</v>
+        <v>7999.6</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2878,16 +3183,16 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J57" s="2"/>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B58" s="22">
         <f>USE_MIN*BUDGET</f>
@@ -2899,20 +3204,20 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J58" s="2"/>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B59" s="22">
         <f>BUDGET-TOTAL_SPEND</f>
-        <v>0</v>
+        <v>0.3999999999996362</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -2920,16 +3225,16 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J59" s="2"/>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B60" s="21">
         <f>SM2_Q+SM3_Q+SM6_Q</f>
@@ -2941,16 +3246,16 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J60" s="2"/>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B61" s="25">
         <f>MK41_CELLS*BUILD_AEGIS-AEGIS_CELLS_USED</f>
@@ -2962,20 +3267,20 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J61" s="2"/>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B62" s="23">
         <f>PAC3_Q/16+MSE_Q/12</f>
-        <v>2.625</v>
+        <v>41.541666666666671</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -2983,20 +3288,20 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J62" s="2"/>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B63" s="23">
         <f>PATRIOT_LAUNCHERS*PATRIOT_BATTERIES-PATRIOT_LAUNCHERS_USED</f>
-        <v>3.375</v>
+        <v>6.4583333333333286</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -3004,20 +3309,20 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J63" s="2"/>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B64" s="21">
         <f>THAAD_CAP*BUILD_THAAD-THAAD_Q</f>
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -3025,20 +3330,20 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J64" s="2"/>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B65" s="26">
         <f>SUMPRODUCT(W,D)/SUMPRODUCT(W,RAID_SIZE)</f>
-        <v>0.73568826890615724</v>
+        <v>0.97322318060097501</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -3046,10 +3351,10 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J65" s="2"/>
     </row>
@@ -3067,37 +3372,37 @@
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B67" s="21">
-        <f t="shared" ref="B67:G67" si="2">B13-B45</f>
-        <v>458</v>
+        <f t="shared" ref="B67:G67" si="2">B13*B160-B45</f>
+        <v>1678</v>
       </c>
       <c r="C67" s="21">
         <f t="shared" si="2"/>
-        <v>500</v>
+        <v>1743</v>
       </c>
       <c r="D67" s="21">
         <f t="shared" si="2"/>
-        <v>457</v>
+        <v>2000</v>
       </c>
       <c r="E67" s="21">
         <f t="shared" si="2"/>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F67" s="21">
         <f t="shared" si="2"/>
-        <v>439</v>
+        <v>2000</v>
       </c>
       <c r="G67" s="21">
         <f t="shared" si="2"/>
-        <v>465</v>
+        <v>1904</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J67" s="2"/>
     </row>
@@ -3115,7 +3420,7 @@
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3129,7 +3434,7 @@
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>5</v>
@@ -3153,151 +3458,151 @@
         <v>11</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J70" s="2"/>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" s="27">
+        <f>IF(B9=0,0,B$17*IF(B$121=0,0,B$121*(1-EXP(-(B$123+B147)/B$121))-B$125)/B$7)</f>
+        <v>1.2414366916300577E-2</v>
+      </c>
+      <c r="C71" s="27">
+        <f>IF(C9=0,0,B$17*IF(B$121=0,0,B$121*(1-EXP(-(B$123+C147)/B$121))-B$125)/C$7)</f>
+        <v>1.093646609293146E-2</v>
+      </c>
+      <c r="D71" s="27">
+        <f>IF(D9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+D147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+D147)/B$122))-B$126))/D$7)</f>
+        <v>3.6167840622293021E-3</v>
+      </c>
+      <c r="E71" s="27">
+        <f>IF(E9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+E147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+E147)/B$122))-B$126))/E$7)</f>
+        <v>1.6463497344197898E-3</v>
+      </c>
+      <c r="F71" s="27">
+        <f>IF(F9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+F147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+F147)/B$122))-B$126))/F$7)</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="27">
+        <f>IF(G9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+G147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+G147)/B$122))-B$126))/G$7)</f>
+        <v>7.0126958153148298E-3</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B71" s="27">
-        <f>IF(B9=0,0,B$17*IF(B$121=0,0,B$121*(1-EXP(-(B$123+B9)/B$121))-B$125)/B$7)</f>
-        <v>0.11527858852493315</v>
-      </c>
-      <c r="C71" s="27">
-        <f>IF(C9=0,0,B$17*IF(B$121=0,0,B$121*(1-EXP(-(B$123+C9)/B$121))-B$125)/C$7)</f>
-        <v>0.10463216464616658</v>
-      </c>
-      <c r="D71" s="27">
-        <f>IF(D9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+D9)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+D9)/B$122))-B$126))/D$7)</f>
-        <v>0.12033062825594243</v>
-      </c>
-      <c r="E71" s="27">
-        <f>IF(E9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+E9)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+E9)/B$122))-B$126))/E$7)</f>
-        <v>5.4148782715174093E-2</v>
-      </c>
-      <c r="F71" s="27">
-        <f>IF(F9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+F9)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+F9)/B$122))-B$126))/F$7)</f>
-        <v>0</v>
-      </c>
-      <c r="G71" s="27">
-        <f>IF(G9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+G9)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+G9)/B$122))-B$126))/G$7)</f>
-        <v>0.28414463848304228</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="J71" s="2"/>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B72" s="27">
-        <f>IF(B10=0,0,C$17*IF(C$121=0,0,C$121*(1-EXP(-(C$123+B10)/C$121))-C$125)/B$7)</f>
-        <v>9.711281812964831E-2</v>
+        <f>IF(B10=0,0,C$17*IF(C$121=0,0,C$121*(1-EXP(-(C$123+B148)/C$121))-C$125)/B$7)</f>
+        <v>6.1536945126876332E-3</v>
       </c>
       <c r="C72" s="27">
-        <f>IF(C10=0,0,C$17*IF(C$121=0,0,C$121*(1-EXP(-(C$123+C10)/C$121))-C$125)/C$7)</f>
-        <v>8.0731911677497201E-2</v>
+        <f>IF(C10=0,0,C$17*IF(C$121=0,0,C$121*(1-EXP(-(C$123+C148)/C$121))-C$125)/C$7)</f>
+        <v>5.4211118326057718E-3</v>
       </c>
       <c r="D72" s="27">
-        <f>IF(D10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+D10)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+D10)/C$122))-C$126))/D$7)</f>
+        <f>IF(D10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+D148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+D148)/C$122))-C$126))/D$7)</f>
         <v>0</v>
       </c>
       <c r="E72" s="27">
-        <f>IF(E10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+E10)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+E10)/C$122))-C$126))/E$7)</f>
+        <f>IF(E10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+E148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+E148)/C$122))-C$126))/E$7)</f>
         <v>0</v>
       </c>
       <c r="F72" s="27">
-        <f>IF(F10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+F10)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+F10)/C$122))-C$126))/F$7)</f>
-        <v>0.46903794251755393</v>
+        <f>IF(F10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+F148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+F148)/C$122))-C$126))/F$7)</f>
+        <v>1.1106668144850852E-2</v>
       </c>
       <c r="G72" s="27">
-        <f>IF(G10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+G10)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+G10)/C$122))-C$126))/G$7)</f>
-        <v>0.23248056970194869</v>
+        <f>IF(G10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+G148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+G148)/C$122))-C$126))/G$7)</f>
+        <v>3.4761327781594265E-3</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J72" s="2"/>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B73" s="27">
-        <f>IF(B11=0,0,D$17*IF(D$121=0,0,D$121*(1-EXP(-(D$123+B11)/D$121))-D$125)/B$7)</f>
-        <v>0.10654419276024869</v>
+        <f>IF(B11=0,0,D$17*IF(D$121=0,0,D$121*(1-EXP(-(D$123+B149)/D$121))-D$125)/B$7)</f>
+        <v>4.5940973902900539E-3</v>
       </c>
       <c r="C73" s="27">
-        <f>IF(C11=0,0,D$17*IF(D$121=0,0,D$121*(1-EXP(-(D$123+C11)/D$121))-D$125)/C$7)</f>
-        <v>8.2250565010110896E-2</v>
+        <f>IF(C11=0,0,D$17*IF(D$121=0,0,D$121*(1-EXP(-(D$123+C149)/D$121))-D$125)/C$7)</f>
+        <v>4.0471810343031423E-3</v>
       </c>
       <c r="D73" s="27">
-        <f>IF(D11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+D11)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+D11)/D$122))-D$126))/D$7)</f>
+        <f>IF(D11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+D149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+D149)/D$122))-D$126))/D$7)</f>
         <v>0</v>
       </c>
       <c r="E73" s="27">
-        <f>IF(E11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+E11)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+E11)/D$122))-D$126))/E$7)</f>
+        <f>IF(E11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+E149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+E149)/D$122))-D$126))/E$7)</f>
         <v>0</v>
       </c>
       <c r="F73" s="27">
-        <f>IF(F11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+F11)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+F11)/D$122))-D$126))/F$7)</f>
-        <v>0.46583032994850093</v>
+        <f>IF(F11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+F149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+F149)/D$122))-D$126))/F$7)</f>
+        <v>8.2917855336942445E-3</v>
       </c>
       <c r="G73" s="27">
-        <f>IF(G11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+G11)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+G11)/D$122))-D$126))/G$7)</f>
-        <v>0.22956035900559282</v>
+        <f>IF(G11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+G149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+G149)/D$122))-D$126))/G$7)</f>
+        <v>2.5951389838279695E-3</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J73" s="2"/>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B74" s="27">
-        <f>IF(B12=0,0,E$17*IF(E$121=0,0,E$121*(1-EXP(-(E$123+B12)/E$121))-E$125)/B$7)</f>
-        <v>0.11503586265301927</v>
+        <f>IF(B12=0,0,E$17*IF(E$121=0,0,E$121*(1-EXP(-(E$123+B150)/E$121))-E$125)/B$7)</f>
+        <v>0</v>
       </c>
       <c r="C74" s="27">
-        <f>IF(C12=0,0,E$17*IF(E$121=0,0,E$121*(1-EXP(-(E$123+C12)/E$121))-E$125)/C$7)</f>
+        <f>IF(C12=0,0,E$17*IF(E$121=0,0,E$121*(1-EXP(-(E$123+C150)/E$121))-E$125)/C$7)</f>
         <v>0</v>
       </c>
       <c r="D74" s="27">
-        <f>IF(D12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+D12)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+D12)/E$122))-E$126))/D$7)</f>
+        <f>IF(D12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+D150)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+D150)/E$122))-E$126))/D$7)</f>
         <v>0</v>
       </c>
       <c r="E74" s="27">
-        <f>IF(E12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+E12)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+E12)/E$122))-E$126))/E$7)</f>
+        <f>IF(E12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+E150)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+E150)/E$122))-E$126))/E$7)</f>
         <v>0</v>
       </c>
       <c r="F74" s="27">
-        <f>IF(F12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+F12)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+F12)/E$122))-E$126))/F$7)</f>
-        <v>0.42089803662194791</v>
+        <f>IF(F12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+F150)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+F150)/E$122))-E$126))/F$7)</f>
+        <v>0</v>
       </c>
       <c r="G74" s="27">
-        <f>IF(G12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+G12)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+G12)/E$122))-E$126))/G$7)</f>
-        <v>0.19576652866137112</v>
+        <f>IF(G12=0,0,E$17*MAX(IF(E$121=0,0,E$121*(1-EXP(-(E$123+G150)/E$121))-E$125),IF(E$122=0,0,E$122*(1-EXP(-(E$124+G150)/E$122))-E$126))/G$7)</f>
+        <v>2.7771526183699477E-2</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J74" s="2"/>
     </row>
@@ -3315,7 +3620,7 @@
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3341,7 +3646,7 @@
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3355,10 +3660,10 @@
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -3367,13 +3672,13 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J79" s="2"/>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B80" s="2" t="b">
         <f>TOTAL_SPEND&lt;=BUDGET+0.001</f>
@@ -3386,13 +3691,13 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J80" s="2"/>
     </row>
     <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B81" s="2" t="b">
         <f>TOTAL_SPEND&gt;=SPEND_FLOOR-0.001</f>
@@ -3405,13 +3710,13 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J81" s="2"/>
     </row>
     <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B82" s="2" t="b">
         <f>AEGIS_CELL_SLACK&gt;=-0.001</f>
@@ -3424,13 +3729,13 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J82" s="2"/>
     </row>
     <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B83" s="2" t="b">
         <f>PATRIOT_SLACK&gt;=-0.001</f>
@@ -3443,13 +3748,13 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J83" s="2"/>
     </row>
     <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B84" s="2" t="b">
         <f>THAAD_SLACK&gt;=-0.001</f>
@@ -3462,13 +3767,13 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J84" s="2"/>
     </row>
     <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B85" s="2" t="b">
         <f>MIN(CAP_SLACK)&gt;=0</f>
@@ -3481,13 +3786,13 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J85" s="2"/>
     </row>
     <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B86" s="2" t="b">
         <f>SUMPRODUCT(--(D&lt;MIN_REQUIRED-0.001))=0</f>
@@ -3500,13 +3805,13 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J86" s="2"/>
     </row>
     <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B87" s="2" t="b">
         <f>SUMPRODUCT(--(B9:G12=0),B35:G38)+SUMPRODUCT(--(B9:G12=0),B108:G111)=0</f>
@@ -3519,13 +3824,13 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J87" s="2"/>
     </row>
     <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B88" s="2" t="b">
         <f>SUMPRODUCT(--(B35:G38&lt;&gt;ROUND(B35:G38,0)))+SUMPRODUCT(--(B108:G111&lt;&gt;ROUND(B108:G111,0)))=0</f>
@@ -3538,16 +3843,16 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J88" s="2"/>
     </row>
     <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B89" s="7" t="b">
-        <f>AND(B80:B88,B130:B134)</f>
+        <f>AND(B80:B88,B130:B134,B171:B174)</f>
         <v>1</v>
       </c>
       <c r="C89" s="2"/>
@@ -3573,7 +3878,7 @@
     </row>
     <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -3587,16 +3892,16 @@
     </row>
     <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="D92" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -3607,7 +3912,7 @@
     </row>
     <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B93" s="27">
         <f>20*(1-EXP(-7/20))</f>
@@ -3629,7 +3934,7 @@
     </row>
     <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B94" s="27">
         <f>20*(1-EXP(-7.7/20))</f>
@@ -3651,7 +3956,7 @@
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B95" s="27">
         <f>96/16</f>
@@ -3673,7 +3978,7 @@
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B96" s="27">
         <f>72/12</f>
@@ -3695,7 +4000,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -3711,7 +4016,7 @@
         <v>4</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
@@ -3727,7 +4032,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B100" s="30">
         <v>16</v>
@@ -3738,15 +4043,15 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B101" s="30">
         <v>2</v>
@@ -3757,15 +4062,15 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B102" s="30">
         <v>8</v>
@@ -3776,15 +4081,15 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B103" s="30">
         <v>16</v>
@@ -3795,15 +4100,15 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B104" s="30">
         <v>16</v>
@@ -3814,15 +4119,15 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3835,7 +4140,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>5</v>
@@ -3859,18 +4164,18 @@
         <v>11</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B108" s="19">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C108" s="19">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="D108" s="19">
         <v>0</v>
@@ -3885,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B109" s="19">
-        <v>12</v>
+        <v>217</v>
       </c>
       <c r="C109" s="19">
         <v>0</v>
@@ -3914,18 +4219,18 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B110" s="19">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C110" s="19">
         <v>0</v>
@@ -3943,18 +4248,18 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B111" s="19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C111" s="19">
         <v>0</v>
@@ -3969,18 +4274,18 @@
         <v>0</v>
       </c>
       <c r="G111" s="19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3996,7 +4301,7 @@
         <v>4</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
@@ -4007,16 +4312,16 @@
         <v>11</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B115" s="31">
         <f>MIN(SITES,SITES_PER_PATRIOT*PATRIOT_BATTERIES)</f>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -4024,19 +4329,19 @@
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B116" s="32">
         <f>PATRIOT_SITES_COVERED/SITES</f>
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -4044,19 +4349,19 @@
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B117" s="31">
         <f>SITES-PATRIOT_SITES_COVERED</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -4064,19 +4369,19 @@
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B118" s="21">
         <f>100000*PATRIOT_SITES_COVERED-SUM(QC)</f>
-        <v>199958</v>
+        <v>1599325</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -4084,10 +4389,10 @@
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -4095,203 +4400,203 @@
         <v>4</v>
       </c>
       <c r="B120" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="E120" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D120" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F120" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B121" s="33">
         <f>B19*$B$116</f>
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C121" s="33">
         <f>C19*$B$116</f>
-        <v>3.75</v>
+        <v>30</v>
       </c>
       <c r="D121" s="33">
         <f>D19*$B$116</f>
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="E121" s="33">
         <f>E19*$B$116</f>
-        <v>6.25</v>
+        <v>50</v>
       </c>
       <c r="F121" s="33">
         <f t="shared" ref="F121:F126" si="3">SUM(B121:E121)</f>
-        <v>16.25</v>
+        <v>130</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B122" s="33">
         <f>B19*(1-$B$116)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C122" s="33">
         <f>C19*(1-$B$116)</f>
-        <v>26.25</v>
+        <v>0</v>
       </c>
       <c r="D122" s="33">
         <f>D19*(1-$B$116)</f>
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="E122" s="33">
         <f>E19*(1-$B$116)</f>
-        <v>43.75</v>
+        <v>0</v>
       </c>
       <c r="F122" s="33">
         <f t="shared" si="3"/>
-        <v>113.75</v>
+        <v>0</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B123" s="23">
-        <f>SUMPRODUCT($B$9:$G$9,$B$108:$G$108)</f>
-        <v>13.2</v>
+        <f>SUMPRODUCT($B$147:$G$147,$B$108:$G$108)</f>
+        <v>200.31953518182419</v>
       </c>
       <c r="C123" s="23">
-        <f>SUMPRODUCT($B$10:$G$10,$B$109:$G$109)</f>
-        <v>8.3999999999999986</v>
+        <f>SUMPRODUCT($B$148:$G$148,$B$109:$G$109)</f>
+        <v>150.41293818150814</v>
       </c>
       <c r="D123" s="23">
-        <f>SUMPRODUCT($B$11:$G$11,$B$110:$G$110)</f>
-        <v>2.25</v>
+        <f>SUMPRODUCT($B$149:$G$149,$B$110:$G$110)</f>
+        <v>50.599744180876009</v>
       </c>
       <c r="E123" s="23">
-        <f>SUMPRODUCT($B$12:$G$12,$B$111:$G$111)</f>
-        <v>4.25</v>
+        <f>SUMPRODUCT($B$150:$G$150,$B$111:$G$111)</f>
+        <v>66.542129333754744</v>
       </c>
       <c r="F123" s="23">
         <f t="shared" si="3"/>
-        <v>28.099999999999998</v>
+        <v>467.87434687796315</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B124" s="23">
-        <f>SUMPRODUCT($B$9:$G$9,$B$35:$G$35)</f>
-        <v>55.4</v>
+        <f>SUMPRODUCT($B$147:$G$147,$B$35:$G$35)</f>
+        <v>0</v>
       </c>
       <c r="C124" s="23">
-        <f>SUMPRODUCT($B$10:$G$10,$B$36:$G$36)</f>
-        <v>36</v>
+        <f>SUMPRODUCT($B$148:$G$148,$B$36:$G$36)</f>
+        <v>0</v>
       </c>
       <c r="D124" s="23">
-        <f>SUMPRODUCT($B$11:$G$11,$B$37:$G$37)</f>
-        <v>10.4</v>
+        <f>SUMPRODUCT($B$149:$G$149,$B$37:$G$37)</f>
+        <v>0</v>
       </c>
       <c r="E124" s="23">
-        <f>SUMPRODUCT($B$12:$G$12,$B$38:$G$38)</f>
+        <f>SUMPRODUCT($B$150:$G$150,$B$38:$G$38)</f>
         <v>0</v>
       </c>
       <c r="F124" s="23">
         <f t="shared" si="3"/>
-        <v>101.80000000000001</v>
+        <v>0</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B125" s="23">
         <f t="shared" ref="B125:E126" si="4">IF(B121=0,0,B121*(1-EXP(-B123/B121)))</f>
-        <v>4.6431936522180699</v>
+        <v>39.732626554474187</v>
       </c>
       <c r="C125" s="23">
         <f t="shared" si="4"/>
-        <v>3.3507806085778018</v>
+        <v>29.800624884152146</v>
       </c>
       <c r="D125" s="23">
         <f t="shared" si="4"/>
-        <v>1.0433763897230168</v>
+        <v>9.9365427815346692</v>
       </c>
       <c r="E125" s="23">
         <f t="shared" si="4"/>
-        <v>3.0836437977150655</v>
+        <v>36.787274492982746</v>
       </c>
       <c r="F125" s="23">
         <f t="shared" si="3"/>
-        <v>12.120994448233954</v>
+        <v>116.25706871314375</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B126" s="23">
         <f t="shared" si="4"/>
-        <v>27.811439675639356</v>
+        <v>0</v>
       </c>
       <c r="C126" s="23">
         <f t="shared" si="4"/>
-        <v>19.589214519525807</v>
+        <v>0</v>
       </c>
       <c r="D126" s="23">
         <f t="shared" si="4"/>
-        <v>6.0842584560602999</v>
+        <v>0</v>
       </c>
       <c r="E126" s="23">
         <f t="shared" si="4"/>
@@ -4299,19 +4604,19 @@
       </c>
       <c r="F126" s="23">
         <f t="shared" si="3"/>
-        <v>53.484912651225457</v>
+        <v>0</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -4324,10 +4629,10 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -4336,12 +4641,12 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B130" s="2" t="b">
         <f>AND(PATRIOT_BATTERIES&gt;=0,PATRIOT_BATTERIES&lt;=PATRIOT_MAX,PATRIOT_BATTERIES=ROUND(PATRIOT_BATTERIES,0))</f>
@@ -4354,12 +4659,12 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B131" s="2" t="b">
         <f>SITES_PER_PATRIOT*PATRIOT_BATTERIES&lt;=SITES</f>
@@ -4372,12 +4677,12 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B132" s="2" t="b">
         <f>SUM(B35:C38)=0</f>
@@ -4390,12 +4695,12 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B133" s="2" t="b">
         <f>IF(PATRIOT_SITES_COVERED=0,SUM(QC)=0,TRUE)</f>
@@ -4408,12 +4713,12 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B134" s="2" t="b">
         <f>AND(AEGIS_SITES=SITES,THAAD_SITES=SITES)</f>
@@ -4426,12 +4731,12 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -4444,16 +4749,16 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="D137" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
@@ -4463,7 +4768,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B138" s="27">
         <f>MIN(16,2*8)/16</f>
@@ -4484,7 +4789,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B139" s="27">
         <f>40*(MIN(16,2*8)/16)</f>
@@ -4505,7 +4810,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B140" s="27">
         <f>8*6*16</f>
@@ -4526,7 +4831,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B141" s="27">
         <f>50*(1-MIN(16,2*4)/16)</f>
@@ -4545,37 +4850,1842 @@
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
     </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B142" s="27">
+        <f>1*(1-EXP(-(-LN(1-0.5))*2))</f>
+        <v>0.75</v>
+      </c>
+      <c r="C142" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="2" t="b">
+        <f>ROUND(B142,3)=C142</f>
+        <v>1</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B143" s="27">
+        <f>20*(1-EXP(-(-LN(1-0.5))*20/20))</f>
+        <v>10</v>
+      </c>
+      <c r="C143" s="10">
+        <v>10</v>
+      </c>
+      <c r="D143" s="2" t="b">
+        <f>ROUND(B143,3)=C143</f>
+        <v>1</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B147" s="27">
+        <f t="shared" ref="B147:G150" si="5">IF(B9&gt;=1,50,-LN(1-B9))</f>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="C147" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="D147" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="E147" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="F147" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G147" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B148" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="C148" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="D148" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E148" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="G148" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B149" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="C149" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="D149" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E149" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="G149" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B150" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C150" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D150" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E150" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F150" s="27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G150" s="27">
+        <f t="shared" si="5"/>
+        <v>0.69314718055994529</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="6"/>
+      <c r="H153" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B154" s="30">
+        <v>3</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B157" s="30">
+        <v>0</v>
+      </c>
+      <c r="C157" s="30">
+        <v>1</v>
+      </c>
+      <c r="D157" s="30">
+        <v>0</v>
+      </c>
+      <c r="E157" s="30">
+        <v>0</v>
+      </c>
+      <c r="F157" s="30">
+        <v>0</v>
+      </c>
+      <c r="G157" s="30">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B158" s="30">
+        <v>0</v>
+      </c>
+      <c r="C158" s="30">
+        <v>0</v>
+      </c>
+      <c r="D158" s="30">
+        <v>1</v>
+      </c>
+      <c r="E158" s="30">
+        <v>1</v>
+      </c>
+      <c r="F158" s="30">
+        <v>0</v>
+      </c>
+      <c r="G158" s="30">
+        <v>1</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B159" s="30">
+        <v>1</v>
+      </c>
+      <c r="C159" s="30">
+        <v>1</v>
+      </c>
+      <c r="D159" s="30">
+        <v>1</v>
+      </c>
+      <c r="E159" s="30">
+        <v>1</v>
+      </c>
+      <c r="F159" s="30">
+        <v>1</v>
+      </c>
+      <c r="G159" s="30">
+        <v>1</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B160" s="31">
+        <f t="shared" ref="B160:G160" si="6">INDEX(B$157:B$159,OPTION)</f>
+        <v>1</v>
+      </c>
+      <c r="C160" s="31">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="D160" s="31">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E160" s="31">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="F160" s="31">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G160" s="31">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="5"/>
+      <c r="E162" s="5"/>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="5"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C163" s="6"/>
+      <c r="D163" s="6"/>
+      <c r="E163" s="6"/>
+      <c r="F163" s="6"/>
+      <c r="G163" s="6"/>
+      <c r="H163" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B164" s="31">
+        <f>IF(OPTION=1,PATRIOT_MAX,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B165" s="31">
+        <f>IF(OPTION=2,0,PATRIOT_MAX)</f>
+        <v>8</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B166" s="31">
+        <f>IF(OPTION=1,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B167" s="31">
+        <f>IF(OPTION=1,MSE_Q-PATRIOT_LAUNCHERS*12*PATRIOT_BATTERIES,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B171" s="2" t="b">
+        <f>SUMPRODUCT(--(ALLOWED_NOW=0),Q_TOTAL)=0</f>
+        <v>1</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B172" s="2" t="b">
+        <f>AND(PATRIOT_BATTERIES&gt;=PATRIOT_MIN,PATRIOT_BATTERIES&lt;=PATRIOT_MAX_NOW)</f>
+        <v>1</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B173" s="2" t="b">
+        <f>BUILD_AEGIS&lt;=AEGIS_ALLOWED</f>
+        <v>1</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B174" s="2" t="b">
+        <f>MSE_FULL_SLACK=0</f>
+        <v>1</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="whole" showErrorMessage="1" errorTitle="Patriot batteries" error="Whole number from 0 to PATRIOT_MAX (Guam limit)." sqref="C41" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <dataValidations count="2">
+    <dataValidation type="whole" showErrorMessage="1" errorTitle="Patriot batteries" error="Whole number from 0 to PATRIOT_MAX (Guam limit)." sqref="C41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>PATRIOT_MAX</formula2>
+    </dataValidation>
+    <dataValidation type="list" sqref="B154" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>Scenarios!$A$5:$A$7</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>B31</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.65">
+      <c r="A1" s="34" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+    </row>
+    <row r="3" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="str">
+        <f>Scenarios!N13</f>
+        <v>1 - 8 Patriot batteries, MSE only</v>
+      </c>
+      <c r="B6" t="str">
+        <f>Scenarios!B13</f>
+        <v>A ballistic-heavy</v>
+      </c>
+      <c r="C6" s="36">
+        <v>92</v>
+      </c>
+      <c r="D6" s="37">
+        <f>Scenarios!C13*100</f>
+        <v>91.564768170863132</v>
+      </c>
+      <c r="E6" t="b">
+        <f t="shared" ref="E6:E14" si="0">ROUND(D6,0)=C6</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="38">
+        <f>Scenarios!D13</f>
+        <v>5619.2</v>
+      </c>
+      <c r="G6" s="37">
+        <f t="shared" ref="G6:G14" si="1">D6/(F6/1000)</f>
+        <v>16.294982946124559</v>
+      </c>
+      <c r="H6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="str">
+        <f>Scenarios!N14</f>
+        <v>1 - 8 Patriot batteries, MSE only</v>
+      </c>
+      <c r="B7" t="str">
+        <f>Scenarios!B14</f>
+        <v>B cruise-heavy</v>
+      </c>
+      <c r="C7" s="36">
+        <v>89</v>
+      </c>
+      <c r="D7" s="37">
+        <f>Scenarios!C14*100</f>
+        <v>88.496928853866237</v>
+      </c>
+      <c r="E7" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="38">
+        <f>Scenarios!D14</f>
+        <v>5619.2</v>
+      </c>
+      <c r="G7" s="37">
+        <f t="shared" si="1"/>
+        <v>15.749026347854896</v>
+      </c>
+      <c r="H7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="str">
+        <f>Scenarios!N15</f>
+        <v>1 - 8 Patriot batteries, MSE only</v>
+      </c>
+      <c r="B8" t="str">
+        <f>Scenarios!B15</f>
+        <v>C drone saturation</v>
+      </c>
+      <c r="C8" s="36">
+        <v>49</v>
+      </c>
+      <c r="D8" s="37">
+        <f>Scenarios!C15*100</f>
+        <v>49.000734304430935</v>
+      </c>
+      <c r="E8" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F8" s="38">
+        <f>Scenarios!D15</f>
+        <v>5619.2</v>
+      </c>
+      <c r="G8" s="37">
+        <f t="shared" si="1"/>
+        <v>8.7202331834479878</v>
+      </c>
+      <c r="H8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="str">
+        <f>Scenarios!N16</f>
+        <v>2 - current Guam plan</v>
+      </c>
+      <c r="B9" t="str">
+        <f>Scenarios!B16</f>
+        <v>A ballistic-heavy</v>
+      </c>
+      <c r="C9" s="36">
+        <v>68</v>
+      </c>
+      <c r="D9" s="37">
+        <f>Scenarios!C16*100</f>
+        <v>67.50219543148711</v>
+      </c>
+      <c r="E9" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="38">
+        <f>Scenarios!D16</f>
+        <v>4120.5</v>
+      </c>
+      <c r="G9" s="37">
+        <f t="shared" si="1"/>
+        <v>16.382039905712197</v>
+      </c>
+      <c r="H9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="str">
+        <f>Scenarios!N17</f>
+        <v>2 - current Guam plan</v>
+      </c>
+      <c r="B10" t="str">
+        <f>Scenarios!B17</f>
+        <v>B cruise-heavy</v>
+      </c>
+      <c r="C10" s="36">
+        <v>53</v>
+      </c>
+      <c r="D10" s="37">
+        <f>Scenarios!C17*100</f>
+        <v>53.314098651500117</v>
+      </c>
+      <c r="E10" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F10" s="38">
+        <f>Scenarios!D17</f>
+        <v>3138.4</v>
+      </c>
+      <c r="G10" s="37">
+        <f t="shared" si="1"/>
+        <v>16.987668446182806</v>
+      </c>
+      <c r="H10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="str">
+        <f>Scenarios!N18</f>
+        <v>2 - current Guam plan</v>
+      </c>
+      <c r="B11" t="str">
+        <f>Scenarios!B18</f>
+        <v>C drone saturation</v>
+      </c>
+      <c r="C11" s="36">
+        <v>43</v>
+      </c>
+      <c r="D11" s="37">
+        <f>Scenarios!C18*100</f>
+        <v>42.504531621732674</v>
+      </c>
+      <c r="E11" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F11" s="38">
+        <f>Scenarios!D18</f>
+        <v>3138.4</v>
+      </c>
+      <c r="G11" s="37">
+        <f t="shared" si="1"/>
+        <v>13.543376122142707</v>
+      </c>
+      <c r="H11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="str">
+        <f>Scenarios!N19</f>
+        <v>3 - optimal mix (up to 8 batteries)</v>
+      </c>
+      <c r="B12" t="str">
+        <f>Scenarios!B19</f>
+        <v>A ballistic-heavy</v>
+      </c>
+      <c r="C12" s="36">
+        <v>97</v>
+      </c>
+      <c r="D12" s="37">
+        <f>Scenarios!C19*100</f>
+        <v>97.322318060097501</v>
+      </c>
+      <c r="E12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="38">
+        <f>Scenarios!D19</f>
+        <v>7999.6</v>
+      </c>
+      <c r="G12" s="37">
+        <f t="shared" si="1"/>
+        <v>12.165898052414809</v>
+      </c>
+      <c r="H12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="str">
+        <f>Scenarios!N20</f>
+        <v>3 - optimal mix (up to 8 batteries)</v>
+      </c>
+      <c r="B13" t="str">
+        <f>Scenarios!B20</f>
+        <v>B cruise-heavy</v>
+      </c>
+      <c r="C13" s="36">
+        <v>95</v>
+      </c>
+      <c r="D13" s="37">
+        <f>Scenarios!C20*100</f>
+        <v>94.901427402312876</v>
+      </c>
+      <c r="E13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="38">
+        <f>Scenarios!D20</f>
+        <v>7999.8</v>
+      </c>
+      <c r="G13" s="37">
+        <f t="shared" si="1"/>
+        <v>11.8629749996641</v>
+      </c>
+      <c r="H13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="str">
+        <f>Scenarios!N21</f>
+        <v>3 - optimal mix (up to 8 batteries)</v>
+      </c>
+      <c r="B14" t="str">
+        <f>Scenarios!B21</f>
+        <v>C drone saturation</v>
+      </c>
+      <c r="C14" s="36">
+        <v>59</v>
+      </c>
+      <c r="D14" s="37">
+        <f>Scenarios!C21*100</f>
+        <v>58.955297540037236</v>
+      </c>
+      <c r="E14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F14" s="38">
+        <f>Scenarios!D21</f>
+        <v>7616.6</v>
+      </c>
+      <c r="G14" s="37">
+        <f t="shared" si="1"/>
+        <v>7.7403693957982878</v>
+      </c>
+      <c r="H14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="E16" s="39" t="b">
+        <f>AND(E6:E14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="39" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>299</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="str">
+        <f>A6</f>
+        <v>1 - 8 Patriot batteries, MSE only</v>
+      </c>
+      <c r="B20" s="36">
+        <v>5.6</v>
+      </c>
+      <c r="C20" s="36">
+        <v>5.6</v>
+      </c>
+      <c r="D20">
+        <f>ROUND(MIN(F6:F8)/1000,1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="E20">
+        <f>ROUND(MAX(F6:F8)/1000,1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="F20" t="b">
+        <f>AND(D20=B20,E20=C20)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="str">
+        <f>A9</f>
+        <v>2 - current Guam plan</v>
+      </c>
+      <c r="B21" s="36">
+        <v>3.1</v>
+      </c>
+      <c r="C21" s="36">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D21">
+        <f>ROUND(MIN(F9:F11)/1000,1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="E21">
+        <f>ROUND(MAX(F9:F11)/1000,1)</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F21" t="b">
+        <f>AND(D21=B21,E21=C21)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="str">
+        <f>A12</f>
+        <v>3 - optimal mix (up to 8 batteries)</v>
+      </c>
+      <c r="B22" s="36">
+        <v>7.6</v>
+      </c>
+      <c r="C22" s="36">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <f>ROUND(MIN(F12:F14)/1000,1)</f>
+        <v>7.6</v>
+      </c>
+      <c r="E22">
+        <f>ROUND(MAX(F12:F14)/1000,1)</f>
+        <v>8</v>
+      </c>
+      <c r="F22" t="b">
+        <f>AND(D22=B22,E22=C22)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A25" s="41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+    </row>
+    <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="36">
+        <v>2000</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="42">
+        <v>55.536000000000001</v>
+      </c>
+      <c r="D28" s="43">
+        <v>1998.7</v>
+      </c>
+      <c r="E28" s="37">
+        <f t="shared" ref="E28:E51" si="2">C28/(D28/1000)</f>
+        <v>27.786060939610746</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="36">
+        <v>2000</v>
+      </c>
+      <c r="B29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" s="42">
+        <v>41.706000000000003</v>
+      </c>
+      <c r="D29" s="43">
+        <v>1999</v>
+      </c>
+      <c r="E29" s="37">
+        <f t="shared" si="2"/>
+        <v>20.863431715857928</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="36">
+        <v>2000</v>
+      </c>
+      <c r="B30" t="s">
+        <v>308</v>
+      </c>
+      <c r="C30" s="42">
+        <v>28.375</v>
+      </c>
+      <c r="D30" s="43">
+        <v>1999.1</v>
+      </c>
+      <c r="E30" s="37">
+        <f t="shared" si="2"/>
+        <v>14.193887249262168</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="36">
+        <v>3000</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="42">
+        <v>70.349000000000004</v>
+      </c>
+      <c r="D31" s="43">
+        <v>2997.7</v>
+      </c>
+      <c r="E31" s="37">
+        <f t="shared" si="2"/>
+        <v>23.467658538212632</v>
+      </c>
+      <c r="F31" s="37">
+        <f t="shared" ref="F31:F51" si="3">(C31-C28)/((D31-D28)/1000)</f>
+        <v>14.827827827827834</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="36">
+        <v>3000</v>
+      </c>
+      <c r="B32" t="s">
+        <v>307</v>
+      </c>
+      <c r="C32" s="42">
+        <v>57.332999999999998</v>
+      </c>
+      <c r="D32" s="43">
+        <v>2999.7</v>
+      </c>
+      <c r="E32" s="37">
+        <f t="shared" si="2"/>
+        <v>19.112911291129112</v>
+      </c>
+      <c r="F32" s="37">
+        <f t="shared" si="3"/>
+        <v>15.616068751873685</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="36">
+        <v>3000</v>
+      </c>
+      <c r="B33" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="42">
+        <v>43.46</v>
+      </c>
+      <c r="D33" s="43">
+        <v>2999.6</v>
+      </c>
+      <c r="E33" s="37">
+        <f t="shared" si="2"/>
+        <v>14.488598479797306</v>
+      </c>
+      <c r="F33" s="37">
+        <f t="shared" si="3"/>
+        <v>15.077461269365319</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="36">
+        <v>4000</v>
+      </c>
+      <c r="B34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="42">
+        <v>82.463999999999999</v>
+      </c>
+      <c r="D34" s="43">
+        <v>3999</v>
+      </c>
+      <c r="E34" s="37">
+        <f t="shared" si="2"/>
+        <v>20.621155288822205</v>
+      </c>
+      <c r="F34" s="37">
+        <f t="shared" si="3"/>
+        <v>12.099270947767895</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="36">
+        <v>4000</v>
+      </c>
+      <c r="B35" t="s">
+        <v>307</v>
+      </c>
+      <c r="C35" s="42">
+        <v>72.915999999999997</v>
+      </c>
+      <c r="D35" s="43">
+        <v>3999.9</v>
+      </c>
+      <c r="E35" s="37">
+        <f t="shared" si="2"/>
+        <v>18.229455736393408</v>
+      </c>
+      <c r="F35" s="37">
+        <f t="shared" si="3"/>
+        <v>15.579884023195357</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="36">
+        <v>4000</v>
+      </c>
+      <c r="B36" t="s">
+        <v>308</v>
+      </c>
+      <c r="C36" s="42">
+        <v>47.491999999999997</v>
+      </c>
+      <c r="D36" s="43">
+        <v>3999.5</v>
+      </c>
+      <c r="E36" s="37">
+        <f t="shared" si="2"/>
+        <v>11.874484310538817</v>
+      </c>
+      <c r="F36" s="37">
+        <f t="shared" si="3"/>
+        <v>4.0324032403240286</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="36">
+        <v>5000</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="42">
+        <v>90.805999999999997</v>
+      </c>
+      <c r="D37" s="43">
+        <v>4998.2</v>
+      </c>
+      <c r="E37" s="37">
+        <f t="shared" si="2"/>
+        <v>18.167740386539155</v>
+      </c>
+      <c r="F37" s="37">
+        <f t="shared" si="3"/>
+        <v>8.348678943154523</v>
+      </c>
+      <c r="G37">
+        <v>8</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="36">
+        <v>5000</v>
+      </c>
+      <c r="B38" t="s">
+        <v>307</v>
+      </c>
+      <c r="C38" s="42">
+        <v>86.616</v>
+      </c>
+      <c r="D38" s="43">
+        <v>4998.2</v>
+      </c>
+      <c r="E38" s="37">
+        <f t="shared" si="2"/>
+        <v>17.329438597895244</v>
+      </c>
+      <c r="F38" s="37">
+        <f t="shared" si="3"/>
+        <v>13.723329660422724</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="36">
+        <v>5000</v>
+      </c>
+      <c r="B39" t="s">
+        <v>308</v>
+      </c>
+      <c r="C39" s="42">
+        <v>51.335000000000001</v>
+      </c>
+      <c r="D39" s="43">
+        <v>4999.1000000000004</v>
+      </c>
+      <c r="E39" s="37">
+        <f t="shared" si="2"/>
+        <v>10.268848392710687</v>
+      </c>
+      <c r="F39" s="37">
+        <f t="shared" si="3"/>
+        <v>3.8445378151260523</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="36">
+        <v>5619</v>
+      </c>
+      <c r="B40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="42">
+        <v>91.573999999999998</v>
+      </c>
+      <c r="D40" s="43">
+        <v>5378.8</v>
+      </c>
+      <c r="E40" s="37">
+        <f t="shared" si="2"/>
+        <v>17.024986985944821</v>
+      </c>
+      <c r="F40" s="37">
+        <f t="shared" si="3"/>
+        <v>2.0178665265370466</v>
+      </c>
+      <c r="G40">
+        <v>8</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="36">
+        <v>5619</v>
+      </c>
+      <c r="B41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C41" s="42">
+        <v>89.570999999999998</v>
+      </c>
+      <c r="D41" s="43">
+        <v>5616.1</v>
+      </c>
+      <c r="E41" s="37">
+        <f t="shared" si="2"/>
+        <v>15.94896814515411</v>
+      </c>
+      <c r="F41" s="37">
+        <f t="shared" si="3"/>
+        <v>4.7823272374170509</v>
+      </c>
+      <c r="G41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="36">
+        <v>5619</v>
+      </c>
+      <c r="B42" t="s">
+        <v>308</v>
+      </c>
+      <c r="C42" s="42">
+        <v>53.997999999999998</v>
+      </c>
+      <c r="D42" s="43">
+        <v>5618</v>
+      </c>
+      <c r="E42" s="37">
+        <f t="shared" si="2"/>
+        <v>9.6116055535777853</v>
+      </c>
+      <c r="F42" s="37">
+        <f t="shared" si="3"/>
+        <v>4.3027952819518474</v>
+      </c>
+      <c r="G42">
+        <v>6</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="36">
+        <v>6000</v>
+      </c>
+      <c r="B43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="42">
+        <v>91.686000000000007</v>
+      </c>
+      <c r="D43" s="43">
+        <v>5996.3</v>
+      </c>
+      <c r="E43" s="37">
+        <f t="shared" si="2"/>
+        <v>15.290429097943735</v>
+      </c>
+      <c r="F43" s="37">
+        <f t="shared" si="3"/>
+        <v>0.18137651821863801</v>
+      </c>
+      <c r="G43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="36">
+        <v>6000</v>
+      </c>
+      <c r="B44" t="s">
+        <v>307</v>
+      </c>
+      <c r="C44" s="42">
+        <v>90.347999999999999</v>
+      </c>
+      <c r="D44" s="43">
+        <v>5997.2</v>
+      </c>
+      <c r="E44" s="37">
+        <f t="shared" si="2"/>
+        <v>15.065030347495499</v>
+      </c>
+      <c r="F44" s="37">
+        <f t="shared" si="3"/>
+        <v>2.0388349514563164</v>
+      </c>
+      <c r="G44">
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="36">
+        <v>6000</v>
+      </c>
+      <c r="B45" t="s">
+        <v>308</v>
+      </c>
+      <c r="C45" s="42">
+        <v>55.103000000000002</v>
+      </c>
+      <c r="D45" s="43">
+        <v>5999.6</v>
+      </c>
+      <c r="E45" s="37">
+        <f t="shared" si="2"/>
+        <v>9.1844456297086481</v>
+      </c>
+      <c r="F45" s="37">
+        <f t="shared" si="3"/>
+        <v>2.8957023060796723</v>
+      </c>
+      <c r="G45">
+        <v>6</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="36">
+        <v>7000</v>
+      </c>
+      <c r="B46" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="42">
+        <v>95.212000000000003</v>
+      </c>
+      <c r="D46" s="43">
+        <v>6999.9</v>
+      </c>
+      <c r="E46" s="37">
+        <f t="shared" si="2"/>
+        <v>13.601908598694269</v>
+      </c>
+      <c r="F46" s="37">
+        <f t="shared" si="3"/>
+        <v>3.5133519330410508</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="36">
+        <v>7000</v>
+      </c>
+      <c r="B47" t="s">
+        <v>307</v>
+      </c>
+      <c r="C47" s="42">
+        <v>91.424000000000007</v>
+      </c>
+      <c r="D47" s="43">
+        <v>6999.3</v>
+      </c>
+      <c r="E47" s="37">
+        <f t="shared" si="2"/>
+        <v>13.061877616333064</v>
+      </c>
+      <c r="F47" s="37">
+        <f t="shared" si="3"/>
+        <v>1.0737451352160534</v>
+      </c>
+      <c r="G47">
+        <v>7</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="36">
+        <v>7000</v>
+      </c>
+      <c r="B48" t="s">
+        <v>308</v>
+      </c>
+      <c r="C48" s="42">
+        <v>58.83</v>
+      </c>
+      <c r="D48" s="43">
+        <v>6997.9</v>
+      </c>
+      <c r="E48" s="37">
+        <f t="shared" si="2"/>
+        <v>8.4068077566126984</v>
+      </c>
+      <c r="F48" s="37">
+        <f t="shared" si="3"/>
+        <v>3.7333466893719316</v>
+      </c>
+      <c r="G48">
+        <v>8</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="36">
+        <v>8000</v>
+      </c>
+      <c r="B49" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="42">
+        <v>97.322000000000003</v>
+      </c>
+      <c r="D49" s="43">
+        <v>7999.6</v>
+      </c>
+      <c r="E49" s="37">
+        <f t="shared" si="2"/>
+        <v>12.165858292914645</v>
+      </c>
+      <c r="F49" s="37">
+        <f t="shared" si="3"/>
+        <v>2.1106331899569852</v>
+      </c>
+      <c r="G49">
+        <v>8</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="36">
+        <v>8000</v>
+      </c>
+      <c r="B50" t="s">
+        <v>307</v>
+      </c>
+      <c r="C50" s="42">
+        <v>94.900999999999996</v>
+      </c>
+      <c r="D50" s="43">
+        <v>7999.8</v>
+      </c>
+      <c r="E50" s="37">
+        <f t="shared" si="2"/>
+        <v>11.862921573039324</v>
+      </c>
+      <c r="F50" s="37">
+        <f t="shared" si="3"/>
+        <v>3.4752623688155819</v>
+      </c>
+      <c r="G50">
+        <v>8</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="36">
+        <v>8000</v>
+      </c>
+      <c r="B51" t="s">
+        <v>308</v>
+      </c>
+      <c r="C51" s="42">
+        <v>58.954999999999998</v>
+      </c>
+      <c r="D51" s="43">
+        <v>7616.6</v>
+      </c>
+      <c r="E51" s="37">
+        <f t="shared" si="2"/>
+        <v>7.740330331118872</v>
+      </c>
+      <c r="F51" s="37">
+        <f t="shared" si="3"/>
+        <v>0.2020365282042991</v>
+      </c>
+      <c r="G51">
+        <v>8</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4587,41 +6697,42 @@
     <col min="9" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="12" width="8" customWidth="1"/>
+    <col min="14" max="14" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F4" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" s="10">
         <v>40</v>
@@ -4636,12 +6747,12 @@
         <v>50</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="B6" s="10">
         <v>15</v>
@@ -4656,12 +6767,12 @@
         <v>60</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="B7" s="10">
         <v>10</v>
@@ -4676,37 +6787,37 @@
         <v>300</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>5</v>
@@ -4727,361 +6838,388 @@
         <v>10</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>320</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="28">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C13" s="29">
-        <v>0.4853250527556624</v>
+        <v>0.91564768170863131</v>
       </c>
       <c r="D13" s="28">
-        <v>2000</v>
+        <v>5619.2</v>
       </c>
       <c r="E13" s="9">
         <v>0</v>
       </c>
       <c r="F13" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G13" s="9">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H13" s="9">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>16</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" s="29">
+        <v>0.8849692885386623</v>
+      </c>
+      <c r="D14" s="28">
+        <v>5619.2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>8</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>576</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>16</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C15" s="29">
+        <v>0.49000734304430932</v>
+      </c>
+      <c r="D15" s="28">
+        <v>5619.2</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>8</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>576</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>16</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="29">
+        <v>0.67502195431487111</v>
+      </c>
+      <c r="D16" s="28">
+        <v>4120.5</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
         <v>48</v>
       </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="28">
-        <v>2000</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="29">
-        <v>0.29684408633790221</v>
-      </c>
-      <c r="D14" s="28">
-        <v>1999.8</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9">
-        <v>1</v>
-      </c>
-      <c r="G14" s="9">
-        <v>86</v>
-      </c>
-      <c r="H14" s="9">
-        <v>1</v>
-      </c>
-      <c r="I14" s="9">
-        <v>44</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="28">
-        <v>2000</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="29">
-        <v>0.25363700608451961</v>
-      </c>
-      <c r="D15" s="28">
-        <v>1999.5</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9">
-        <v>1</v>
-      </c>
-      <c r="G15" s="9">
+      <c r="J16" s="9">
+        <v>46</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>50</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C17" s="29">
+        <v>0.53314098651500119</v>
+      </c>
+      <c r="D17" s="28">
+        <v>3138.4</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>48</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9">
+        <v>96</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18" s="29">
+        <v>0.42504531621732672</v>
+      </c>
+      <c r="D18" s="28">
+        <v>3138.4</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>48</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>96</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="29">
+        <v>0.97322318060097501</v>
+      </c>
+      <c r="D19" s="28">
+        <v>7999.6</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9">
+        <v>8</v>
+      </c>
+      <c r="G19" s="9">
+        <v>322</v>
+      </c>
+      <c r="H19" s="9">
+        <v>257</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>96</v>
+      </c>
+      <c r="M19" s="9">
+        <v>16</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="28">
+        <v>8000</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="29">
+        <v>0.94901427402312877</v>
+      </c>
+      <c r="D20" s="28">
+        <v>7999.8</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9">
+        <v>8</v>
+      </c>
+      <c r="G20" s="9">
+        <v>615</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>1</v>
+      </c>
+      <c r="L20" s="9">
         <v>95</v>
       </c>
-      <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="9">
-        <v>42</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="28">
-        <v>4000</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="29">
-        <v>0.73568826890615724</v>
-      </c>
-      <c r="D16" s="28">
-        <v>4000</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9">
-        <v>42</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>43</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>61</v>
-      </c>
-      <c r="L16" s="9">
-        <v>35</v>
-      </c>
-      <c r="M16" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="28">
-        <v>4000</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C17" s="29">
-        <v>0.63546000553217674</v>
-      </c>
-      <c r="D17" s="28">
-        <v>3999.2</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9">
-        <v>75</v>
-      </c>
-      <c r="H17" s="9">
-        <v>1</v>
-      </c>
-      <c r="I17" s="9">
-        <v>40</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>96</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="28">
-        <v>4000</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="29">
-        <v>0.50717482431389693</v>
-      </c>
-      <c r="D18" s="28">
-        <v>3998.5</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9">
-        <v>1</v>
-      </c>
-      <c r="G18" s="9">
-        <v>96</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>34</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>91</v>
-      </c>
-      <c r="L18" s="9">
-        <v>5</v>
-      </c>
-      <c r="M18" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="28">
-        <v>6000</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="29">
-        <v>0.83428592598411877</v>
-      </c>
-      <c r="D19" s="28">
-        <v>6000</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9">
-        <v>2</v>
-      </c>
-      <c r="G19" s="9">
-        <v>191</v>
-      </c>
-      <c r="H19" s="9">
-        <v>0</v>
-      </c>
-      <c r="I19" s="9">
-        <v>48</v>
-      </c>
-      <c r="J19" s="9">
-        <v>7</v>
-      </c>
-      <c r="K19" s="9">
-        <v>4</v>
-      </c>
-      <c r="L19" s="9">
-        <v>85</v>
-      </c>
-      <c r="M19" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="28">
-        <v>6000</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C20" s="29">
-        <v>0.73646413540311828</v>
-      </c>
-      <c r="D20" s="28">
-        <v>5832.8</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9">
-        <v>2</v>
-      </c>
-      <c r="G20" s="9">
-        <v>192</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9">
-        <v>48</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>96</v>
-      </c>
       <c r="M20" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="28">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="C21" s="29">
-        <v>0.58871066022494301</v>
+        <v>0.58955297540037233</v>
       </c>
       <c r="D21" s="28">
-        <v>5754.6</v>
+        <v>7616.6</v>
       </c>
       <c r="E21" s="9">
         <v>1</v>
       </c>
       <c r="F21" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G21" s="9">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="H21" s="9">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="I21" s="9">
         <v>48</v>
@@ -5090,87 +7228,64 @@
         <v>0</v>
       </c>
       <c r="K21" s="9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L21" s="9">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="M21" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="28">
-        <v>6000</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" s="29">
-        <v>0.83428592598411877</v>
-      </c>
-      <c r="D22" s="28">
-        <v>6000</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9">
-        <v>2</v>
-      </c>
-      <c r="G22" s="9">
-        <v>191</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9">
-        <v>48</v>
-      </c>
-      <c r="J22" s="9">
-        <v>7</v>
-      </c>
-      <c r="K22" s="9">
-        <v>4</v>
-      </c>
-      <c r="L22" s="9">
-        <v>85</v>
-      </c>
-      <c r="M22" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="28"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>255</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -5179,9 +7294,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B23"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5190,111 +7305,111 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="7" t="s">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>258</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>260</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
-        <v>261</v>
+        <v>333</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>262</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>266</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7" t="s">
-        <v>267</v>
+        <v>339</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>268</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7" t="s">
-        <v>269</v>
+        <v>341</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>270</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
-        <v>271</v>
+        <v>343</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>272</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>276</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>278</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7" t="s">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>280</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7" t="s">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>282</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5303,58 +7418,82 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>283</v>
+        <v>355</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>286</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7" t="s">
-        <v>287</v>
+        <v>359</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>288</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7" t="s">
-        <v>289</v>
+        <v>361</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>290</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7" t="s">
-        <v>291</v>
+        <v>363</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>292</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7" t="s">
-        <v>293</v>
+        <v>365</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>294</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7" t="s">
-        <v>295</v>
+        <v>367</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>296</v>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richi\AppData\Local\Temp\mx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18976A0C-88FC-4CDF-883A-7A9AE54E329A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEECCF18-1DEC-4292-B3C8-F2C57E659AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,13 +140,13 @@
     <definedName name="solver_lhs9" localSheetId="0" hidden="1">Model!$B$67:$G$67</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_msl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_msl" localSheetId="0">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0">20</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">Model!$B$65</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="0">2</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">4</definedName>
     <definedName name="solver_rel10" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel11" localSheetId="0">4</definedName>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="398">
   <si>
     <t>Guam interceptor loadout - economic research model (inputs from Table 1 of the paper, 2026-10-10; site constraints, kill rate and options added)</t>
   </si>
@@ -1121,7 +1121,7 @@
     <t>Table 2 of the paper: where each number comes from</t>
   </si>
   <si>
-    <t>Each Table 2 cell is the PROTECTION cell (Model!B65) after setting OPTION (Model!B154), ACTIVE_RAID (Model!B31) and BUDGET (Model!B23 = 8,000) and solving. The reference values on the Scenarios sheet (rows 13-21) come from an external integer solver (reference-optimizer.py, in this folder); column E checks each of the paper's rounded values against them (FALSE = the paper's number differs from the workbook).</t>
+    <t>Each Table 2 cell is the PROTECTION cell (Model!B65) after setting OPTION (Model!B154), ACTIVE_RAID (Model!B31) and BUDGET (Model!B23 = 8,000) and solving. The reference values on the Scenarios sheet (rows 13-21) come from an external integer solver followed by an exact local search (reference-optimizer.py, in this folder); column E checks each of the paper's rounded values against them (FALSE = the paper's number differs from the workbook).</t>
   </si>
   <si>
     <t>Inputs are Table 1 of the paper; the 50% kill probability, raid sizes, damage weights and the even spread of threats over 16 sites are placeholders. Options 2 and 3 are re-solved for each raid; Option 1 is one fixed purchase.</t>
@@ -1280,6 +1280,75 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Option 1, A ballistic-heavy</t>
+  </si>
+  <si>
+    <t>Yes (same)</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from an evenly spread allocation; code 14: Solver found an integer solution within tolerance; all constraints satisfied; 2.5 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution; code 14: Solver found an integer solution within tolerance; all constraints satisfied; 2.2 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>No: 29.1 points below</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from a rough point (all interceptors in the first class); code 1: Solver converged to the current solution; all constraints satisfied; 1.4 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Option 1, B cruise-heavy</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution; code 0: Solver found a solution; all constraints and optimality conditions satisfied; 2 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Option 1, C drone saturation</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution; code 14: Solver found an integer solution within tolerance; all constraints satisfied; 2.1 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Option 2, A ballistic-heavy</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution; code 0: Solver found a solution; all constraints and optimality conditions satisfied; 1.3 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from a rough point (all interceptors in the first class); code 0: Solver found a solution; all constraints and optimality conditions satisfied; 2.6 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Option 2, B cruise-heavy</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution; code 0: Solver found a solution; all constraints and optimality conditions satisfied; 1.6 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Option 2, C drone saturation</t>
+  </si>
+  <si>
+    <t>Option 3, A ballistic-heavy</t>
+  </si>
+  <si>
+    <t>Did not finish</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution: no result within the 60 s limit plus a 240 s wait; the reference solution is feasible (ALL_VALID TRUE) but Solver could not confirm or improve it. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
+    <t>Option 3, B cruise-heavy</t>
+  </si>
+  <si>
+    <t>Option 3, C drone saturation</t>
+  </si>
+  <si>
+    <t>No: 0.1 points below</t>
+  </si>
+  <si>
+    <t>Excel Solver (GRG Nonlinear), started from the reference solution; code 14: Solver found an integer solution within tolerance; all constraints satisfied; 4.4 s; ALL_VALID True. Run by Claude, 2026-10-10.</t>
+  </si>
+  <si>
     <t>Solver setup (saved in the Model sheet; open Data &gt; Solver to see it)</t>
   </si>
   <si>
@@ -1298,7 +1367,7 @@
     <t>Engine</t>
   </si>
   <si>
-    <t>GRG Nonlinear (the objective uses EXP, so Simplex LP cannot be used), with Multistart on. Integer optimality tolerance 0%. Not run in the build (Solver hangs headless).</t>
+    <t>GRG Nonlinear (the objective uses EXP, so Simplex LP cannot be used); Multistart OFF and Require Bounds OFF (with them ON every Solve stops with 'All variables must have both upper and lower bounds'); integer optimality tolerance 0%; Max Time 60 s. Run from the Solver dialog or SolverSolve.</t>
   </si>
   <si>
     <t>Constraint 1</t>
@@ -1382,7 +1451,7 @@
     <t>Known limits</t>
   </si>
   <si>
-    <t>Inputs are placeholders. Kill probabilities and raid sizes are assumptions, not data, and so is the even spread of threats over the 16 sites. GRG on an integer problem can stop at a local optimum - that is why the external reference results exist.</t>
+    <t>Inputs are placeholders. Kill probabilities and raid sizes are assumptions, not data, and so is the even spread of threats over the 16 sites. GRG with integer variables can stall at a poor point from a bad start and cannot finish the Option 3 problem in reasonable time; that is why the external reference results exist. See the Scenarios sheet, MY SOLVER RUNS, for what Solver did on 2026-10-10.</t>
   </si>
   <si>
     <t>Constraint 11</t>
@@ -1425,13 +1494,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0000%"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1576,7 +1647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1623,6 +1694,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2866,11 +2939,11 @@
       </c>
       <c r="B45" s="21">
         <f t="shared" ref="B45:G45" si="0">SUM(B35:B38)+SUM(B108:B111)</f>
-        <v>322</v>
+        <v>613</v>
       </c>
       <c r="C45" s="21">
         <f t="shared" si="0"/>
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="D45" s="21">
         <f t="shared" si="0"/>
@@ -2902,11 +2975,11 @@
       </c>
       <c r="B46" s="22">
         <f t="shared" ref="B46:G46" si="1">B7*B45</f>
-        <v>1191.4000000000001</v>
+        <v>2268.1</v>
       </c>
       <c r="C46" s="22">
         <f t="shared" si="1"/>
-        <v>1079.4000000000001</v>
+        <v>0</v>
       </c>
       <c r="D46" s="22">
         <f t="shared" si="1"/>
@@ -2978,15 +3051,15 @@
       </c>
       <c r="B49" s="23">
         <f>B123+B124</f>
-        <v>200.31953518182419</v>
+        <v>227.35227522366205</v>
       </c>
       <c r="C49" s="23">
         <f>C123+C124</f>
-        <v>150.41293818150814</v>
+        <v>149.71979100094819</v>
       </c>
       <c r="D49" s="23">
         <f>D123+D124</f>
-        <v>50.599744180876009</v>
+        <v>47.827155458636227</v>
       </c>
       <c r="E49" s="23">
         <f>E123+E124</f>
@@ -3008,15 +3081,15 @@
       </c>
       <c r="B50" s="23">
         <f>B125+B126</f>
-        <v>39.732626554474187</v>
+        <v>39.863976474484978</v>
       </c>
       <c r="C50" s="23">
         <f>C125+C126</f>
-        <v>29.800624884152146</v>
+        <v>29.795964711727471</v>
       </c>
       <c r="D50" s="23">
         <f>D125+D126</f>
-        <v>9.9365427815346692</v>
+        <v>9.9162676982393521</v>
       </c>
       <c r="E50" s="23">
         <f>E125+E126</f>
@@ -3024,7 +3097,7 @@
       </c>
       <c r="F50" s="23">
         <f>SUM(B50:E50)</f>
-        <v>116.25706871314375</v>
+        <v>116.36348337743455</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
@@ -3041,15 +3114,15 @@
       </c>
       <c r="B51" s="24">
         <f>IF(B19=0,0,B50/B19)</f>
-        <v>0.99331566386185466</v>
+        <v>0.99659941186212442</v>
       </c>
       <c r="C51" s="24">
         <f>IF(C19=0,0,C50/C19)</f>
-        <v>0.99335416280507149</v>
+        <v>0.99319882372424906</v>
       </c>
       <c r="D51" s="24">
         <f>IF(D19=0,0,D50/D19)</f>
-        <v>0.99365427815346696</v>
+        <v>0.99162676982393516</v>
       </c>
       <c r="E51" s="24">
         <f>IF(E19=0,0,E50/E19)</f>
@@ -3133,7 +3206,7 @@
       </c>
       <c r="B55" s="22">
         <f>SUMPRODUCT(PRICE,Q_TOTAL)</f>
-        <v>2899.6000000000004</v>
+        <v>2896.8999999999996</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -3175,7 +3248,7 @@
       </c>
       <c r="B57" s="22">
         <f>INTERCEPTOR_SPEND+SYSTEM_SPEND</f>
-        <v>7999.6</v>
+        <v>7996.9</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -3217,7 +3290,7 @@
       </c>
       <c r="B59" s="22">
         <f>BUDGET-TOTAL_SPEND</f>
-        <v>0.3999999999996362</v>
+        <v>3.1000000000003638</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -3280,7 +3353,7 @@
       </c>
       <c r="B62" s="23">
         <f>PAC3_Q/16+MSE_Q/12</f>
-        <v>41.541666666666671</v>
+        <v>38.3125</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -3301,7 +3374,7 @@
       </c>
       <c r="B63" s="23">
         <f>PATRIOT_LAUNCHERS*PATRIOT_BATTERIES-PATRIOT_LAUNCHERS_USED</f>
-        <v>6.4583333333333286</v>
+        <v>9.6875</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -3343,7 +3416,7 @@
       </c>
       <c r="B65" s="26">
         <f>SUMPRODUCT(W,D)/SUMPRODUCT(W,RAID_SIZE)</f>
-        <v>0.97322318060097501</v>
+        <v>0.97511239623348023</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -3376,11 +3449,11 @@
       </c>
       <c r="B67" s="21">
         <f t="shared" ref="B67:G67" si="2">B13*B160-B45</f>
-        <v>1678</v>
+        <v>1387</v>
       </c>
       <c r="C67" s="21">
         <f t="shared" si="2"/>
-        <v>1743</v>
+        <v>2000</v>
       </c>
       <c r="D67" s="21">
         <f t="shared" si="2"/>
@@ -3468,19 +3541,19 @@
       </c>
       <c r="B71" s="27">
         <f>IF(B9=0,0,B$17*IF(B$121=0,0,B$121*(1-EXP(-(B$123+B147)/B$121))-B$125)/B$7)</f>
-        <v>1.2414366916300577E-2</v>
+        <v>6.3156831138342475E-3</v>
       </c>
       <c r="C71" s="27">
         <f>IF(C9=0,0,B$17*IF(B$121=0,0,B$121*(1-EXP(-(B$123+C147)/B$121))-B$125)/C$7)</f>
-        <v>1.093646609293146E-2</v>
+        <v>5.5638160764730276E-3</v>
       </c>
       <c r="D71" s="27">
         <f>IF(D9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+D147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+D147)/B$122))-B$126))/D$7)</f>
-        <v>3.6167840622293021E-3</v>
+        <v>1.8400021670225764E-3</v>
       </c>
       <c r="E71" s="27">
         <f>IF(E9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+E147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+E147)/B$122))-B$126))/E$7)</f>
-        <v>1.6463497344197898E-3</v>
+        <v>8.3756371043680004E-4</v>
       </c>
       <c r="F71" s="27">
         <f>IF(F9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+F147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+F147)/B$122))-B$126))/F$7)</f>
@@ -3488,7 +3561,7 @@
       </c>
       <c r="G71" s="27">
         <f>IF(G9=0,0,B$17*MAX(IF(B$121=0,0,B$121*(1-EXP(-(B$123+G147)/B$121))-B$125),IF(B$122=0,0,B$122*(1-EXP(-(B$124+G147)/B$122))-B$126))/G$7)</f>
-        <v>7.0126958153148298E-3</v>
+        <v>3.5676377894941556E-3</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>135</v>
@@ -3504,11 +3577,11 @@
       </c>
       <c r="B72" s="27">
         <f>IF(B10=0,0,C$17*IF(C$121=0,0,C$121*(1-EXP(-(C$123+B148)/C$121))-C$125)/B$7)</f>
-        <v>6.1536945126876332E-3</v>
+        <v>6.2975303036146872E-3</v>
       </c>
       <c r="C72" s="27">
         <f>IF(C10=0,0,C$17*IF(C$121=0,0,C$121*(1-EXP(-(C$123+C148)/C$121))-C$125)/C$7)</f>
-        <v>5.4211118326057718E-3</v>
+        <v>5.5478243150891291E-3</v>
       </c>
       <c r="D72" s="27">
         <f>IF(D10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+D148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+D148)/C$122))-C$126))/D$7)</f>
@@ -3520,11 +3593,11 @@
       </c>
       <c r="F72" s="27">
         <f>IF(F10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+F148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+F148)/C$122))-C$126))/F$7)</f>
-        <v>1.1106668144850852E-2</v>
+        <v>1.1366274206524071E-2</v>
       </c>
       <c r="G72" s="27">
         <f>IF(G10=0,0,C$17*MAX(IF(C$121=0,0,C$121*(1-EXP(-(C$123+G148)/C$121))-C$125),IF(C$122=0,0,C$122*(1-EXP(-(C$124+G148)/C$122))-C$126))/G$7)</f>
-        <v>3.4761327781594265E-3</v>
+        <v>3.5573835302861595E-3</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>135</v>
@@ -3540,11 +3613,11 @@
       </c>
       <c r="B73" s="27">
         <f>IF(B11=0,0,D$17*IF(D$121=0,0,D$121*(1-EXP(-(D$123+B149)/D$121))-D$125)/B$7)</f>
-        <v>4.5940973902900539E-3</v>
+        <v>6.0619478493491264E-3</v>
       </c>
       <c r="C73" s="27">
         <f>IF(C11=0,0,D$17*IF(D$121=0,0,D$121*(1-EXP(-(D$123+C149)/D$121))-D$125)/C$7)</f>
-        <v>4.0471810343031423E-3</v>
+        <v>5.3402873910932784E-3</v>
       </c>
       <c r="D73" s="27">
         <f>IF(D11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+D149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+D149)/D$122))-D$126))/D$7)</f>
@@ -3556,11 +3629,11 @@
       </c>
       <c r="F73" s="27">
         <f>IF(F11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+F149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+F149)/D$122))-D$126))/F$7)</f>
-        <v>8.2917855336942445E-3</v>
+        <v>1.0941076606142328E-2</v>
       </c>
       <c r="G73" s="27">
         <f>IF(G11=0,0,D$17*MAX(IF(D$121=0,0,D$121*(1-EXP(-(D$123+G149)/D$121))-D$125),IF(D$122=0,0,D$122*(1-EXP(-(D$124+G149)/D$122))-D$126))/G$7)</f>
-        <v>2.5951389838279695E-3</v>
+        <v>3.424306418716301E-3</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>135</v>
@@ -4172,10 +4245,10 @@
         <v>189</v>
       </c>
       <c r="B108" s="19">
-        <v>32</v>
+        <v>328</v>
       </c>
       <c r="C108" s="19">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="D108" s="19">
         <v>0</v>
@@ -4201,7 +4274,7 @@
         <v>191</v>
       </c>
       <c r="B109" s="19">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C109" s="19">
         <v>0</v>
@@ -4230,7 +4303,7 @@
         <v>192</v>
       </c>
       <c r="B110" s="19">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C110" s="19">
         <v>0</v>
@@ -4381,7 +4454,7 @@
       </c>
       <c r="B118" s="21">
         <f>100000*PATRIOT_SITES_COVERED-SUM(QC)</f>
-        <v>1599325</v>
+        <v>1599291</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -4492,15 +4565,15 @@
       </c>
       <c r="B123" s="23">
         <f>SUMPRODUCT($B$147:$G$147,$B$108:$G$108)</f>
-        <v>200.31953518182419</v>
+        <v>227.35227522366205</v>
       </c>
       <c r="C123" s="23">
         <f>SUMPRODUCT($B$148:$G$148,$B$109:$G$109)</f>
-        <v>150.41293818150814</v>
+        <v>149.71979100094819</v>
       </c>
       <c r="D123" s="23">
         <f>SUMPRODUCT($B$149:$G$149,$B$110:$G$110)</f>
-        <v>50.599744180876009</v>
+        <v>47.827155458636227</v>
       </c>
       <c r="E123" s="23">
         <f>SUMPRODUCT($B$150:$G$150,$B$111:$G$111)</f>
@@ -4508,7 +4581,7 @@
       </c>
       <c r="F123" s="23">
         <f t="shared" si="3"/>
-        <v>467.87434687796315</v>
+        <v>491.44135101700124</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2" t="s">
@@ -4556,15 +4629,15 @@
       </c>
       <c r="B125" s="23">
         <f t="shared" ref="B125:E126" si="4">IF(B121=0,0,B121*(1-EXP(-B123/B121)))</f>
-        <v>39.732626554474187</v>
+        <v>39.863976474484978</v>
       </c>
       <c r="C125" s="23">
         <f t="shared" si="4"/>
-        <v>29.800624884152146</v>
+        <v>29.795964711727471</v>
       </c>
       <c r="D125" s="23">
         <f t="shared" si="4"/>
-        <v>9.9365427815346692</v>
+        <v>9.9162676982393521</v>
       </c>
       <c r="E125" s="23">
         <f t="shared" si="4"/>
@@ -4572,7 +4645,7 @@
       </c>
       <c r="F125" s="23">
         <f t="shared" si="3"/>
-        <v>116.25706871314375</v>
+        <v>116.36348337743455</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2" t="s">
@@ -5527,28 +5600,28 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="35" t="s">
@@ -5590,7 +5663,7 @@
       </c>
       <c r="D6" s="37">
         <f>Scenarios!C13*100</f>
-        <v>91.564768170863132</v>
+        <v>91.602876170564841</v>
       </c>
       <c r="E6" t="b">
         <f t="shared" ref="E6:E14" si="0">ROUND(D6,0)=C6</f>
@@ -5602,7 +5675,7 @@
       </c>
       <c r="G6" s="37">
         <f t="shared" ref="G6:G14" si="1">D6/(F6/1000)</f>
-        <v>16.294982946124559</v>
+        <v>16.301764694363047</v>
       </c>
       <c r="H6" t="s">
         <v>285</v>
@@ -5622,11 +5695,11 @@
       </c>
       <c r="D7" s="37">
         <f>Scenarios!C14*100</f>
-        <v>88.496928853866237</v>
+        <v>88.578726426429583</v>
       </c>
       <c r="E7" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="38">
         <f>Scenarios!D14</f>
@@ -5634,7 +5707,7 @@
       </c>
       <c r="G7" s="37">
         <f t="shared" si="1"/>
-        <v>15.749026347854896</v>
+        <v>15.763583148211415</v>
       </c>
       <c r="H7" t="s">
         <v>286</v>
@@ -5654,7 +5727,7 @@
       </c>
       <c r="D8" s="37">
         <f>Scenarios!C15*100</f>
-        <v>49.000734304430935</v>
+        <v>49.13668977663518</v>
       </c>
       <c r="E8" t="b">
         <f t="shared" si="0"/>
@@ -5666,7 +5739,7 @@
       </c>
       <c r="G8" s="37">
         <f t="shared" si="1"/>
-        <v>8.7202331834479878</v>
+        <v>8.7444279927098485</v>
       </c>
       <c r="H8" t="s">
         <v>287</v>
@@ -5694,11 +5767,11 @@
       </c>
       <c r="F9" s="38">
         <f>Scenarios!D16</f>
-        <v>4120.5</v>
+        <v>3138.4</v>
       </c>
       <c r="G9" s="37">
         <f t="shared" si="1"/>
-        <v>16.382039905712197</v>
+        <v>21.508474200703258</v>
       </c>
       <c r="H9" t="s">
         <v>288</v>
@@ -5778,11 +5851,11 @@
         <v>A ballistic-heavy</v>
       </c>
       <c r="C12" s="36">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="37">
         <f>Scenarios!C19*100</f>
-        <v>97.322318060097501</v>
+        <v>97.511239623348018</v>
       </c>
       <c r="E12" t="b">
         <f t="shared" si="0"/>
@@ -5790,11 +5863,11 @@
       </c>
       <c r="F12" s="38">
         <f>Scenarios!D19</f>
-        <v>7999.6</v>
+        <v>7996.9</v>
       </c>
       <c r="G12" s="37">
         <f t="shared" si="1"/>
-        <v>12.165898052414809</v>
+        <v>12.193629984537512</v>
       </c>
       <c r="H12" t="s">
         <v>291</v>
@@ -5814,7 +5887,7 @@
       </c>
       <c r="D13" s="37">
         <f>Scenarios!C20*100</f>
-        <v>94.901427402312876</v>
+        <v>94.956451958619326</v>
       </c>
       <c r="E13" t="b">
         <f t="shared" si="0"/>
@@ -5826,7 +5899,7 @@
       </c>
       <c r="G13" s="37">
         <f t="shared" si="1"/>
-        <v>11.8629749996641</v>
+        <v>11.869853241158443</v>
       </c>
       <c r="H13" t="s">
         <v>292</v>
@@ -5846,7 +5919,7 @@
       </c>
       <c r="D14" s="37">
         <f>Scenarios!C21*100</f>
-        <v>58.955297540037236</v>
+        <v>59.258142564089475</v>
       </c>
       <c r="E14" t="b">
         <f t="shared" si="0"/>
@@ -5854,11 +5927,11 @@
       </c>
       <c r="F14" s="38">
         <f>Scenarios!D21</f>
-        <v>7616.6</v>
+        <v>7996.9</v>
       </c>
       <c r="G14" s="37">
         <f t="shared" si="1"/>
-        <v>7.7403693957982878</v>
+        <v>7.4101392494703546</v>
       </c>
       <c r="H14" t="s">
         <v>293</v>
@@ -5870,7 +5943,7 @@
       </c>
       <c r="E16" s="39" t="b">
         <f>AND(E6:E14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5931,7 +6004,7 @@
         <v>3.1</v>
       </c>
       <c r="C21" s="36">
-        <v>4.0999999999999996</v>
+        <v>3.1</v>
       </c>
       <c r="D21">
         <f>ROUND(MIN(F9:F11)/1000,1)</f>
@@ -5939,7 +6012,7 @@
       </c>
       <c r="E21">
         <f>ROUND(MAX(F9:F11)/1000,1)</f>
-        <v>4.0999999999999996</v>
+        <v>3.1</v>
       </c>
       <c r="F21" t="b">
         <f>AND(D21=B21,E21=C21)</f>
@@ -5952,14 +6025,14 @@
         <v>3 - optimal mix (up to 8 batteries)</v>
       </c>
       <c r="B22" s="36">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="36">
         <v>8</v>
       </c>
       <c r="D22">
         <f>ROUND(MIN(F12:F14)/1000,1)</f>
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <f>ROUND(MAX(F12:F14)/1000,1)</f>
@@ -5976,16 +6049,16 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="46" t="s">
         <v>301</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
     </row>
     <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="35" t="s">
@@ -6069,14 +6142,14 @@
         <v>308</v>
       </c>
       <c r="C30" s="42">
-        <v>28.375</v>
+        <v>28.376999999999999</v>
       </c>
       <c r="D30" s="43">
         <v>1999.1</v>
       </c>
       <c r="E30" s="37">
         <f t="shared" si="2"/>
-        <v>14.193887249262168</v>
+        <v>14.194887699464759</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -6093,18 +6166,18 @@
         <v>71</v>
       </c>
       <c r="C31" s="42">
-        <v>70.349000000000004</v>
+        <v>70.350999999999999</v>
       </c>
       <c r="D31" s="43">
         <v>2997.7</v>
       </c>
       <c r="E31" s="37">
         <f t="shared" si="2"/>
-        <v>23.467658538212632</v>
+        <v>23.468325716382559</v>
       </c>
       <c r="F31" s="37">
         <f t="shared" ref="F31:F51" si="3">(C31-C28)/((D31-D28)/1000)</f>
-        <v>14.827827827827834</v>
+        <v>14.829829829829832</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -6149,18 +6222,18 @@
         <v>308</v>
       </c>
       <c r="C33" s="42">
-        <v>43.46</v>
+        <v>43.460999999999999</v>
       </c>
       <c r="D33" s="43">
-        <v>2999.6</v>
+        <v>2998.6</v>
       </c>
       <c r="E33" s="37">
         <f t="shared" si="2"/>
-        <v>14.488598479797306</v>
+        <v>14.493763756419664</v>
       </c>
       <c r="F33" s="37">
         <f t="shared" si="3"/>
-        <v>15.077461269365319</v>
+        <v>15.091545772886443</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -6188,7 +6261,7 @@
       </c>
       <c r="F34" s="37">
         <f t="shared" si="3"/>
-        <v>12.099270947767895</v>
+        <v>12.097273544392289</v>
       </c>
       <c r="G34">
         <v>7</v>
@@ -6208,15 +6281,15 @@
         <v>72.915999999999997</v>
       </c>
       <c r="D35" s="43">
-        <v>3999.9</v>
+        <v>3999.4</v>
       </c>
       <c r="E35" s="37">
         <f t="shared" si="2"/>
-        <v>18.229455736393408</v>
+        <v>18.231734760214032</v>
       </c>
       <c r="F35" s="37">
         <f t="shared" si="3"/>
-        <v>15.579884023195357</v>
+        <v>15.587676302890861</v>
       </c>
       <c r="G35">
         <v>7</v>
@@ -6233,18 +6306,18 @@
         <v>308</v>
       </c>
       <c r="C36" s="42">
-        <v>47.491999999999997</v>
+        <v>47.502000000000002</v>
       </c>
       <c r="D36" s="43">
         <v>3999.5</v>
       </c>
       <c r="E36" s="37">
         <f t="shared" si="2"/>
-        <v>11.874484310538817</v>
+        <v>11.876984623077886</v>
       </c>
       <c r="F36" s="37">
         <f t="shared" si="3"/>
-        <v>4.0324032403240286</v>
+        <v>4.0373663702667635</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -6261,18 +6334,18 @@
         <v>71</v>
       </c>
       <c r="C37" s="42">
-        <v>90.805999999999997</v>
+        <v>90.912000000000006</v>
       </c>
       <c r="D37" s="43">
         <v>4998.2</v>
       </c>
       <c r="E37" s="37">
         <f t="shared" si="2"/>
-        <v>18.167740386539155</v>
+        <v>18.188948021287665</v>
       </c>
       <c r="F37" s="37">
         <f t="shared" si="3"/>
-        <v>8.348678943154523</v>
+        <v>8.4547638110488474</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -6300,7 +6373,7 @@
       </c>
       <c r="F38" s="37">
         <f t="shared" si="3"/>
-        <v>13.723329660422724</v>
+        <v>13.71645975170205</v>
       </c>
       <c r="G38">
         <v>8</v>
@@ -6328,7 +6401,7 @@
       </c>
       <c r="F39" s="37">
         <f t="shared" si="3"/>
-        <v>3.8445378151260523</v>
+        <v>3.834533813525407</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -6345,18 +6418,18 @@
         <v>71</v>
       </c>
       <c r="C40" s="42">
-        <v>91.573999999999998</v>
+        <v>91.887</v>
       </c>
       <c r="D40" s="43">
-        <v>5378.8</v>
+        <v>5616.1</v>
       </c>
       <c r="E40" s="37">
         <f t="shared" si="2"/>
-        <v>17.024986985944821</v>
+        <v>16.361353964494935</v>
       </c>
       <c r="F40" s="37">
         <f t="shared" si="3"/>
-        <v>2.0178665265370466</v>
+        <v>1.5779252306198308</v>
       </c>
       <c r="G40">
         <v>8</v>
@@ -6373,18 +6446,18 @@
         <v>307</v>
       </c>
       <c r="C41" s="42">
-        <v>89.570999999999998</v>
+        <v>89.590999999999994</v>
       </c>
       <c r="D41" s="43">
         <v>5616.1</v>
       </c>
       <c r="E41" s="37">
         <f t="shared" si="2"/>
-        <v>15.94896814515411</v>
+        <v>15.952529335303856</v>
       </c>
       <c r="F41" s="37">
         <f t="shared" si="3"/>
-        <v>4.7823272374170509</v>
+        <v>4.8146949344553995</v>
       </c>
       <c r="G41">
         <v>8</v>
@@ -6401,18 +6474,18 @@
         <v>308</v>
       </c>
       <c r="C42" s="42">
-        <v>53.997999999999998</v>
+        <v>54.005000000000003</v>
       </c>
       <c r="D42" s="43">
         <v>5618</v>
       </c>
       <c r="E42" s="37">
         <f t="shared" si="2"/>
-        <v>9.6116055535777853</v>
+        <v>9.612851548593806</v>
       </c>
       <c r="F42" s="37">
         <f t="shared" si="3"/>
-        <v>4.3027952819518474</v>
+        <v>4.3141056713524044</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -6429,18 +6502,18 @@
         <v>71</v>
       </c>
       <c r="C43" s="42">
-        <v>91.686000000000007</v>
+        <v>92.064999999999998</v>
       </c>
       <c r="D43" s="43">
-        <v>5996.3</v>
+        <v>5997.2</v>
       </c>
       <c r="E43" s="37">
         <f t="shared" si="2"/>
-        <v>15.290429097943735</v>
+        <v>15.351330620956448</v>
       </c>
       <c r="F43" s="37">
         <f t="shared" si="3"/>
-        <v>0.18137651821863801</v>
+        <v>0.46706901075832469</v>
       </c>
       <c r="G43">
         <v>8</v>
@@ -6457,18 +6530,18 @@
         <v>307</v>
       </c>
       <c r="C44" s="42">
-        <v>90.347999999999999</v>
+        <v>90.382999999999996</v>
       </c>
       <c r="D44" s="43">
         <v>5997.2</v>
       </c>
       <c r="E44" s="37">
         <f t="shared" si="2"/>
-        <v>15.065030347495499</v>
+        <v>15.070866404322018</v>
       </c>
       <c r="F44" s="37">
         <f t="shared" si="3"/>
-        <v>2.0388349514563164</v>
+        <v>2.0781946995539302</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -6485,18 +6558,18 @@
         <v>308</v>
       </c>
       <c r="C45" s="42">
-        <v>55.103000000000002</v>
+        <v>55.115000000000002</v>
       </c>
       <c r="D45" s="43">
-        <v>5999.6</v>
+        <v>5997.6</v>
       </c>
       <c r="E45" s="37">
         <f t="shared" si="2"/>
-        <v>9.1844456297086481</v>
+        <v>9.1895091369881285</v>
       </c>
       <c r="F45" s="37">
         <f t="shared" si="3"/>
-        <v>2.8957023060796723</v>
+        <v>2.9241306638566869</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -6513,18 +6586,18 @@
         <v>71</v>
       </c>
       <c r="C46" s="42">
-        <v>95.212000000000003</v>
+        <v>95.257000000000005</v>
       </c>
       <c r="D46" s="43">
         <v>6999.9</v>
       </c>
       <c r="E46" s="37">
         <f t="shared" si="2"/>
-        <v>13.601908598694269</v>
+        <v>13.608337261960887</v>
       </c>
       <c r="F46" s="37">
         <f t="shared" si="3"/>
-        <v>3.5133519330410508</v>
+        <v>3.1834048070210508</v>
       </c>
       <c r="G46">
         <v>7</v>
@@ -6541,18 +6614,18 @@
         <v>307</v>
       </c>
       <c r="C47" s="42">
-        <v>91.424000000000007</v>
+        <v>91.504000000000005</v>
       </c>
       <c r="D47" s="43">
         <v>6999.3</v>
       </c>
       <c r="E47" s="37">
         <f t="shared" si="2"/>
-        <v>13.061877616333064</v>
+        <v>13.073307330733074</v>
       </c>
       <c r="F47" s="37">
         <f t="shared" si="3"/>
-        <v>1.0737451352160534</v>
+        <v>1.1186508332501834</v>
       </c>
       <c r="G47">
         <v>7</v>
@@ -6569,18 +6642,18 @@
         <v>308</v>
       </c>
       <c r="C48" s="42">
-        <v>58.83</v>
+        <v>58.866999999999997</v>
       </c>
       <c r="D48" s="43">
         <v>6997.9</v>
       </c>
       <c r="E48" s="37">
         <f t="shared" si="2"/>
-        <v>8.4068077566126984</v>
+        <v>8.4120950570885551</v>
       </c>
       <c r="F48" s="37">
         <f t="shared" si="3"/>
-        <v>3.7333466893719316</v>
+        <v>3.7508747375787244</v>
       </c>
       <c r="G48">
         <v>8</v>
@@ -6597,18 +6670,18 @@
         <v>71</v>
       </c>
       <c r="C49" s="42">
-        <v>97.322000000000003</v>
+        <v>97.510999999999996</v>
       </c>
       <c r="D49" s="43">
-        <v>7999.6</v>
+        <v>7996.9</v>
       </c>
       <c r="E49" s="37">
         <f t="shared" si="2"/>
-        <v>12.165858292914645</v>
+        <v>12.193600020007754</v>
       </c>
       <c r="F49" s="37">
         <f t="shared" si="3"/>
-        <v>2.1106331899569852</v>
+        <v>2.2607823470411139</v>
       </c>
       <c r="G49">
         <v>8</v>
@@ -6625,18 +6698,18 @@
         <v>307</v>
       </c>
       <c r="C50" s="42">
-        <v>94.900999999999996</v>
+        <v>94.956000000000003</v>
       </c>
       <c r="D50" s="43">
         <v>7999.8</v>
       </c>
       <c r="E50" s="37">
         <f t="shared" si="2"/>
-        <v>11.862921573039324</v>
+        <v>11.869796744918622</v>
       </c>
       <c r="F50" s="37">
         <f t="shared" si="3"/>
-        <v>3.4752623688155819</v>
+        <v>3.4502748625687141</v>
       </c>
       <c r="G50">
         <v>8</v>
@@ -6653,18 +6726,18 @@
         <v>308</v>
       </c>
       <c r="C51" s="42">
-        <v>58.954999999999998</v>
+        <v>59.258000000000003</v>
       </c>
       <c r="D51" s="43">
-        <v>7616.6</v>
+        <v>7996.9</v>
       </c>
       <c r="E51" s="37">
         <f t="shared" si="2"/>
-        <v>7.740330331118872</v>
+        <v>7.4101214220510458</v>
       </c>
       <c r="F51" s="37">
         <f t="shared" si="3"/>
-        <v>0.2020365282042991</v>
+        <v>0.39139139139139673</v>
       </c>
       <c r="G51">
         <v>8</v>
@@ -6685,7 +6758,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6693,7 +6766,7 @@
     <col min="3" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="11" customWidth="1"/>
+    <col min="7" max="8" width="60" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="12" width="8" customWidth="1"/>
@@ -6852,7 +6925,7 @@
         <v>71</v>
       </c>
       <c r="C13" s="29">
-        <v>0.91564768170863131</v>
+        <v>0.9160287617056484</v>
       </c>
       <c r="D13" s="28">
         <v>5619.2</v>
@@ -6896,7 +6969,7 @@
         <v>307</v>
       </c>
       <c r="C14" s="29">
-        <v>0.8849692885386623</v>
+        <v>0.88578726426429588</v>
       </c>
       <c r="D14" s="28">
         <v>5619.2</v>
@@ -6940,7 +7013,7 @@
         <v>308</v>
       </c>
       <c r="C15" s="29">
-        <v>0.49000734304430932</v>
+        <v>0.49136689776635178</v>
       </c>
       <c r="D15" s="28">
         <v>5619.2</v>
@@ -6987,7 +7060,7 @@
         <v>0.67502195431487111</v>
       </c>
       <c r="D16" s="28">
-        <v>4120.5</v>
+        <v>3138.4</v>
       </c>
       <c r="E16" s="9">
         <v>1</v>
@@ -7005,13 +7078,13 @@
         <v>48</v>
       </c>
       <c r="J16" s="9">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
       </c>
       <c r="L16" s="9">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="M16" s="9">
         <v>0</v>
@@ -7116,10 +7189,10 @@
         <v>71</v>
       </c>
       <c r="C19" s="29">
-        <v>0.97322318060097501</v>
+        <v>0.97511239623348023</v>
       </c>
       <c r="D19" s="28">
-        <v>7999.6</v>
+        <v>7996.9</v>
       </c>
       <c r="E19" s="9">
         <v>1</v>
@@ -7128,10 +7201,10 @@
         <v>8</v>
       </c>
       <c r="G19" s="9">
-        <v>322</v>
+        <v>613</v>
       </c>
       <c r="H19" s="9">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9">
         <v>0</v>
@@ -7160,7 +7233,7 @@
         <v>307</v>
       </c>
       <c r="C20" s="29">
-        <v>0.94901427402312877</v>
+        <v>0.94956451958619326</v>
       </c>
       <c r="D20" s="28">
         <v>7999.8</v>
@@ -7204,10 +7277,10 @@
         <v>308</v>
       </c>
       <c r="C21" s="29">
-        <v>0.58955297540037233</v>
+        <v>0.59258142564089478</v>
       </c>
       <c r="D21" s="28">
-        <v>7616.6</v>
+        <v>7996.9</v>
       </c>
       <c r="E21" s="9">
         <v>1</v>
@@ -7216,13 +7289,13 @@
         <v>8</v>
       </c>
       <c r="G21" s="9">
-        <v>98</v>
+        <v>613</v>
       </c>
       <c r="H21" s="9">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -7286,6 +7359,270 @@
       </c>
       <c r="G27" s="6" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="44">
+        <v>0.91602300000000003</v>
+      </c>
+      <c r="E28" s="45">
+        <v>5619.2</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="44">
+        <v>0.91602799999999995</v>
+      </c>
+      <c r="E29" s="45">
+        <v>5619.2</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="44">
+        <v>0.62497100000000005</v>
+      </c>
+      <c r="E30" s="45">
+        <v>5619.2</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="44">
+        <v>0.88578699999999999</v>
+      </c>
+      <c r="E31" s="45">
+        <v>5619.2</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="44">
+        <v>0.491367</v>
+      </c>
+      <c r="E32" s="45">
+        <v>5619.2</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="44">
+        <v>0.67502200000000001</v>
+      </c>
+      <c r="E33" s="45">
+        <v>4120.5</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="44">
+        <v>0.67502200000000001</v>
+      </c>
+      <c r="E34" s="45">
+        <v>3138.4</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0</v>
+      </c>
+      <c r="D35" s="44">
+        <v>0.53314099999999998</v>
+      </c>
+      <c r="E35" s="45">
+        <v>3138.4</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="44">
+        <v>0.42504500000000001</v>
+      </c>
+      <c r="E36" s="45">
+        <v>3138.4</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
+        <v>8000</v>
+      </c>
+      <c r="B37" t="s">
+        <v>344</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>345</v>
+      </c>
+      <c r="G37" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38">
+        <v>8000</v>
+      </c>
+      <c r="B38" t="s">
+        <v>347</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="s">
+        <v>345</v>
+      </c>
+      <c r="G38" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="9">
+        <v>8000</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0</v>
+      </c>
+      <c r="D39" s="44">
+        <v>0.59191800000000006</v>
+      </c>
+      <c r="E39" s="45">
+        <v>7995.1</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -7305,111 +7642,111 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="7" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7418,82 +7755,82 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="7" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
